--- a/astro-site/public/dl/restaurant-schedule-templates/05-pto-vacation-planner.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/05-pto-vacation-planner.xlsx
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -403,6 +403,9 @@
     <xf numFmtId="168" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="8" fillId="9" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -417,6 +420,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -895,7 +901,7 @@
     <row r="7">
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>▸ Absence codes: V=Vacation/PTO · S=Sick · H=Holiday · L=Other leave. They are single letters on purpose: the columns are narrow. In the schedule (file 01 (Restaurant Schedule Template: Weekly &amp; Monthly Staff Rota)) a day off is OFF.</t>
+          <t>▸ Absence codes: V=Vacation/PTO · S=Sick · H=Holiday · L=Other leave. They are single letters on purpose: the columns are narrow. In the schedule (file 01 "Restaurant Schedule Template") a day off is OFF.</t>
         </is>
       </c>
     </row>
@@ -916,7 +922,7 @@
     <row r="10">
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>▸ Also fill in the "Separation / end date" of anyone who will not reach year-end: the entitlement is prorated at BOTH ends, and that number is what goes into the final paycheck (some states require accrued PTO to be paid out; California does, Labor Code §227.3). A seasonal worker from January to June earns 7 days, not 14.</t>
+          <t>▸ Also fill in the "Separation / end date" of anyone who will not reach year-end: the entitlement is prorated at BOTH ends. A seasonal worker from January to June earns 7 days, not 14 — check it against your state's final-pay rule and your own PTO policy (some states require accrued PTO to be paid out; California does, Labor Code §227.3).</t>
         </is>
       </c>
     </row>
@@ -3591,8 +3597,8 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+    <row r="37" ht="24.5" customHeight="1">
+      <c r="A37" s="63" t="inlineStr">
         <is>
           <t>Absences marked in the grid (V, S, L)</t>
         </is>
@@ -3810,8 +3816,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="23" t="inlineStr">
+    <row r="38" ht="24.5" customHeight="1">
+      <c r="A38" s="63" t="inlineStr">
         <is>
           <t>Absences from APPROVED requests</t>
         </is>
@@ -4029,8 +4035,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
+    <row r="39" ht="24.5" customHeight="1">
+      <c r="A39" s="63" t="inlineStr">
         <is>
           <t>Absences in the week (the higher of the two)</t>
         </is>
@@ -4507,13 +4513,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Type a valid date (the Sunday you want the year to start on)." promptTitle="Anchor · Invalid date" prompt="Sunday of WEEK 1 — change it each year and the 52 remaining dates recalculate on their own (each one is the previous + 7). It also drives the year in the title, the balance closing date and the gray band that separates the months." type="custom" errorStyle="stop">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Type a valid date (the Sunday you want the year to start on)." promptTitle="Sunday of week 1" prompt="Sunday of WEEK 1 — change it each year and the 52 remaining dates recalculate on their own (each one is the previous + 7). It also drives the year in the title, the balance closing date and the gray band that separates the months." type="custom" errorStyle="stop">
       <formula1>B5&gt;36526</formula1>
     </dataValidation>
-    <dataValidation sqref="B36:BB36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid season" error="Only High or Normal is accepted." promptTitle="Season · Invalid season" prompt="Type &quot;High&quot; in your peak-demand weeks. An absence in a high-season week lights up red even if it does not exceed the maximum of simultaneous absences." type="custom" errorStyle="stop">
+    <dataValidation sqref="B36:BB36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid season" error="Only High or Normal is accepted." promptTitle="Season" prompt="Type &quot;High&quot; in your peak-demand weeks. An absence in a high-season week lights up red even if it does not exceed the maximum of simultaneous absences." type="custom" errorStyle="stop">
       <formula1>OR(B36="High",B36="Normal")</formula1>
     </dataValidation>
-    <dataValidation sqref="B6:BB35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid absence code" error="Use V, S, H or L. They are single letters because the columns are narrow; in the schedule (file 01 (Restaurant Schedule Template: Weekly &amp; Monthly Staff Rota)) a day off is OFF." promptTitle="kitgp-v2 · Invalid absence code" prompt="Absence codes: V=Vacation/PTO · S=Sick · H=Holiday · L=Other leave." type="list" errorStyle="stop">
+    <dataValidation sqref="B6:BB35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid absence code" error="Use V, S, H or L. They are single letters because the columns are narrow; in the schedule (file 01 &quot;Restaurant Schedule Template&quot;) a day off is OFF." promptTitle="Absence code" prompt="Absence codes: V=Vacation/PTO · S=Sick · H=Holiday · L=Other leave." type="list" errorStyle="stop">
       <formula1>"V,S,H,L,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4608,17 +4614,17 @@
     </row>
     <row r="5">
       <c r="A5" s="42" t="n"/>
-      <c r="B5" s="63" t="n"/>
-      <c r="C5" s="63" t="n"/>
+      <c r="B5" s="64" t="n"/>
+      <c r="C5" s="64" t="n"/>
       <c r="D5" s="44">
         <f>IF(OR($B5="",$C5=""),"",IF($C5&lt;$B5,"⚠ dates reversed",$C5-$B5+1))</f>
         <v/>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="65">
         <f>IFERROR(IF($A5="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A5,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="65">
+      <c r="F5" s="66">
         <f>IFERROR(IF($A5="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A5,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4630,17 +4636,17 @@
     </row>
     <row r="6">
       <c r="A6" s="42" t="n"/>
-      <c r="B6" s="63" t="n"/>
-      <c r="C6" s="63" t="n"/>
+      <c r="B6" s="64" t="n"/>
+      <c r="C6" s="64" t="n"/>
       <c r="D6" s="44">
         <f>IF(OR($B6="",$C6=""),"",IF($C6&lt;$B6,"⚠ dates reversed",$C6-$B6+1))</f>
         <v/>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="65">
         <f>IFERROR(IF($A6="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A6,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="66">
         <f>IFERROR(IF($A6="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A6,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4652,17 +4658,17 @@
     </row>
     <row r="7">
       <c r="A7" s="42" t="n"/>
-      <c r="B7" s="63" t="n"/>
-      <c r="C7" s="63" t="n"/>
+      <c r="B7" s="64" t="n"/>
+      <c r="C7" s="64" t="n"/>
       <c r="D7" s="44">
         <f>IF(OR($B7="",$C7=""),"",IF($C7&lt;$B7,"⚠ dates reversed",$C7-$B7+1))</f>
         <v/>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="65">
         <f>IFERROR(IF($A7="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A7,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="65">
+      <c r="F7" s="66">
         <f>IFERROR(IF($A7="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A7,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4674,17 +4680,17 @@
     </row>
     <row r="8">
       <c r="A8" s="42" t="n"/>
-      <c r="B8" s="63" t="n"/>
-      <c r="C8" s="63" t="n"/>
+      <c r="B8" s="64" t="n"/>
+      <c r="C8" s="64" t="n"/>
       <c r="D8" s="44">
         <f>IF(OR($B8="",$C8=""),"",IF($C8&lt;$B8,"⚠ dates reversed",$C8-$B8+1))</f>
         <v/>
       </c>
-      <c r="E8" s="64">
+      <c r="E8" s="65">
         <f>IFERROR(IF($A8="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A8,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="65">
+      <c r="F8" s="66">
         <f>IFERROR(IF($A8="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A8,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4696,17 +4702,17 @@
     </row>
     <row r="9">
       <c r="A9" s="42" t="n"/>
-      <c r="B9" s="63" t="n"/>
-      <c r="C9" s="63" t="n"/>
+      <c r="B9" s="64" t="n"/>
+      <c r="C9" s="64" t="n"/>
       <c r="D9" s="44">
         <f>IF(OR($B9="",$C9=""),"",IF($C9&lt;$B9,"⚠ dates reversed",$C9-$B9+1))</f>
         <v/>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="65">
         <f>IFERROR(IF($A9="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A9,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="65">
+      <c r="F9" s="66">
         <f>IFERROR(IF($A9="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A9,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4718,17 +4724,17 @@
     </row>
     <row r="10">
       <c r="A10" s="42" t="n"/>
-      <c r="B10" s="63" t="n"/>
-      <c r="C10" s="63" t="n"/>
+      <c r="B10" s="64" t="n"/>
+      <c r="C10" s="64" t="n"/>
       <c r="D10" s="44">
         <f>IF(OR($B10="",$C10=""),"",IF($C10&lt;$B10,"⚠ dates reversed",$C10-$B10+1))</f>
         <v/>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="65">
         <f>IFERROR(IF($A10="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A10,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="65">
+      <c r="F10" s="66">
         <f>IFERROR(IF($A10="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A10,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4740,17 +4746,17 @@
     </row>
     <row r="11">
       <c r="A11" s="42" t="n"/>
-      <c r="B11" s="63" t="n"/>
-      <c r="C11" s="63" t="n"/>
+      <c r="B11" s="64" t="n"/>
+      <c r="C11" s="64" t="n"/>
       <c r="D11" s="44">
         <f>IF(OR($B11="",$C11=""),"",IF($C11&lt;$B11,"⚠ dates reversed",$C11-$B11+1))</f>
         <v/>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="65">
         <f>IFERROR(IF($A11="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A11,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="65">
+      <c r="F11" s="66">
         <f>IFERROR(IF($A11="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A11,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4762,17 +4768,17 @@
     </row>
     <row r="12">
       <c r="A12" s="42" t="n"/>
-      <c r="B12" s="63" t="n"/>
-      <c r="C12" s="63" t="n"/>
+      <c r="B12" s="64" t="n"/>
+      <c r="C12" s="64" t="n"/>
       <c r="D12" s="44">
         <f>IF(OR($B12="",$C12=""),"",IF($C12&lt;$B12,"⚠ dates reversed",$C12-$B12+1))</f>
         <v/>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="65">
         <f>IFERROR(IF($A12="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A12,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="66">
         <f>IFERROR(IF($A12="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A12,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4784,17 +4790,17 @@
     </row>
     <row r="13">
       <c r="A13" s="42" t="n"/>
-      <c r="B13" s="63" t="n"/>
-      <c r="C13" s="63" t="n"/>
+      <c r="B13" s="64" t="n"/>
+      <c r="C13" s="64" t="n"/>
       <c r="D13" s="44">
         <f>IF(OR($B13="",$C13=""),"",IF($C13&lt;$B13,"⚠ dates reversed",$C13-$B13+1))</f>
         <v/>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="65">
         <f>IFERROR(IF($A13="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A13,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="65">
+      <c r="F13" s="66">
         <f>IFERROR(IF($A13="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A13,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4806,17 +4812,17 @@
     </row>
     <row r="14">
       <c r="A14" s="42" t="n"/>
-      <c r="B14" s="63" t="n"/>
-      <c r="C14" s="63" t="n"/>
+      <c r="B14" s="64" t="n"/>
+      <c r="C14" s="64" t="n"/>
       <c r="D14" s="44">
         <f>IF(OR($B14="",$C14=""),"",IF($C14&lt;$B14,"⚠ dates reversed",$C14-$B14+1))</f>
         <v/>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="65">
         <f>IFERROR(IF($A14="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A14,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F14" s="65">
+      <c r="F14" s="66">
         <f>IFERROR(IF($A14="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A14,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4828,17 +4834,17 @@
     </row>
     <row r="15">
       <c r="A15" s="42" t="n"/>
-      <c r="B15" s="63" t="n"/>
-      <c r="C15" s="63" t="n"/>
+      <c r="B15" s="64" t="n"/>
+      <c r="C15" s="64" t="n"/>
       <c r="D15" s="44">
         <f>IF(OR($B15="",$C15=""),"",IF($C15&lt;$B15,"⚠ dates reversed",$C15-$B15+1))</f>
         <v/>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="65">
         <f>IFERROR(IF($A15="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A15,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F15" s="65">
+      <c r="F15" s="66">
         <f>IFERROR(IF($A15="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A15,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4850,17 +4856,17 @@
     </row>
     <row r="16">
       <c r="A16" s="42" t="n"/>
-      <c r="B16" s="63" t="n"/>
-      <c r="C16" s="63" t="n"/>
+      <c r="B16" s="64" t="n"/>
+      <c r="C16" s="64" t="n"/>
       <c r="D16" s="44">
         <f>IF(OR($B16="",$C16=""),"",IF($C16&lt;$B16,"⚠ dates reversed",$C16-$B16+1))</f>
         <v/>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="65">
         <f>IFERROR(IF($A16="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A16,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F16" s="65">
+      <c r="F16" s="66">
         <f>IFERROR(IF($A16="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A16,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4872,17 +4878,17 @@
     </row>
     <row r="17">
       <c r="A17" s="42" t="n"/>
-      <c r="B17" s="63" t="n"/>
-      <c r="C17" s="63" t="n"/>
+      <c r="B17" s="64" t="n"/>
+      <c r="C17" s="64" t="n"/>
       <c r="D17" s="44">
         <f>IF(OR($B17="",$C17=""),"",IF($C17&lt;$B17,"⚠ dates reversed",$C17-$B17+1))</f>
         <v/>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="65">
         <f>IFERROR(IF($A17="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A17,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="66">
         <f>IFERROR(IF($A17="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A17,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4894,17 +4900,17 @@
     </row>
     <row r="18">
       <c r="A18" s="42" t="n"/>
-      <c r="B18" s="63" t="n"/>
-      <c r="C18" s="63" t="n"/>
+      <c r="B18" s="64" t="n"/>
+      <c r="C18" s="64" t="n"/>
       <c r="D18" s="44">
         <f>IF(OR($B18="",$C18=""),"",IF($C18&lt;$B18,"⚠ dates reversed",$C18-$B18+1))</f>
         <v/>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="65">
         <f>IFERROR(IF($A18="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A18,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F18" s="65">
+      <c r="F18" s="66">
         <f>IFERROR(IF($A18="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A18,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4916,17 +4922,17 @@
     </row>
     <row r="19">
       <c r="A19" s="42" t="n"/>
-      <c r="B19" s="63" t="n"/>
-      <c r="C19" s="63" t="n"/>
+      <c r="B19" s="64" t="n"/>
+      <c r="C19" s="64" t="n"/>
       <c r="D19" s="44">
         <f>IF(OR($B19="",$C19=""),"",IF($C19&lt;$B19,"⚠ dates reversed",$C19-$B19+1))</f>
         <v/>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="65">
         <f>IFERROR(IF($A19="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A19,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F19" s="65">
+      <c r="F19" s="66">
         <f>IFERROR(IF($A19="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A19,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4938,17 +4944,17 @@
     </row>
     <row r="20">
       <c r="A20" s="42" t="n"/>
-      <c r="B20" s="63" t="n"/>
-      <c r="C20" s="63" t="n"/>
+      <c r="B20" s="64" t="n"/>
+      <c r="C20" s="64" t="n"/>
       <c r="D20" s="44">
         <f>IF(OR($B20="",$C20=""),"",IF($C20&lt;$B20,"⚠ dates reversed",$C20-$B20+1))</f>
         <v/>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="65">
         <f>IFERROR(IF($A20="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A20,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F20" s="65">
+      <c r="F20" s="66">
         <f>IFERROR(IF($A20="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A20,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4960,17 +4966,17 @@
     </row>
     <row r="21">
       <c r="A21" s="42" t="n"/>
-      <c r="B21" s="63" t="n"/>
-      <c r="C21" s="63" t="n"/>
+      <c r="B21" s="64" t="n"/>
+      <c r="C21" s="64" t="n"/>
       <c r="D21" s="44">
         <f>IF(OR($B21="",$C21=""),"",IF($C21&lt;$B21,"⚠ dates reversed",$C21-$B21+1))</f>
         <v/>
       </c>
-      <c r="E21" s="64">
+      <c r="E21" s="65">
         <f>IFERROR(IF($A21="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A21,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="66">
         <f>IFERROR(IF($A21="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A21,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -4982,17 +4988,17 @@
     </row>
     <row r="22">
       <c r="A22" s="42" t="n"/>
-      <c r="B22" s="63" t="n"/>
-      <c r="C22" s="63" t="n"/>
+      <c r="B22" s="64" t="n"/>
+      <c r="C22" s="64" t="n"/>
       <c r="D22" s="44">
         <f>IF(OR($B22="",$C22=""),"",IF($C22&lt;$B22,"⚠ dates reversed",$C22-$B22+1))</f>
         <v/>
       </c>
-      <c r="E22" s="64">
+      <c r="E22" s="65">
         <f>IFERROR(IF($A22="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A22,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F22" s="65">
+      <c r="F22" s="66">
         <f>IFERROR(IF($A22="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A22,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5004,17 +5010,17 @@
     </row>
     <row r="23">
       <c r="A23" s="42" t="n"/>
-      <c r="B23" s="63" t="n"/>
-      <c r="C23" s="63" t="n"/>
+      <c r="B23" s="64" t="n"/>
+      <c r="C23" s="64" t="n"/>
       <c r="D23" s="44">
         <f>IF(OR($B23="",$C23=""),"",IF($C23&lt;$B23,"⚠ dates reversed",$C23-$B23+1))</f>
         <v/>
       </c>
-      <c r="E23" s="64">
+      <c r="E23" s="65">
         <f>IFERROR(IF($A23="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A23,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="66">
         <f>IFERROR(IF($A23="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A23,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5026,17 +5032,17 @@
     </row>
     <row r="24">
       <c r="A24" s="42" t="n"/>
-      <c r="B24" s="63" t="n"/>
-      <c r="C24" s="63" t="n"/>
+      <c r="B24" s="64" t="n"/>
+      <c r="C24" s="64" t="n"/>
       <c r="D24" s="44">
         <f>IF(OR($B24="",$C24=""),"",IF($C24&lt;$B24,"⚠ dates reversed",$C24-$B24+1))</f>
         <v/>
       </c>
-      <c r="E24" s="64">
+      <c r="E24" s="65">
         <f>IFERROR(IF($A24="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A24,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F24" s="65">
+      <c r="F24" s="66">
         <f>IFERROR(IF($A24="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A24,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5048,17 +5054,17 @@
     </row>
     <row r="25">
       <c r="A25" s="42" t="n"/>
-      <c r="B25" s="63" t="n"/>
-      <c r="C25" s="63" t="n"/>
+      <c r="B25" s="64" t="n"/>
+      <c r="C25" s="64" t="n"/>
       <c r="D25" s="44">
         <f>IF(OR($B25="",$C25=""),"",IF($C25&lt;$B25,"⚠ dates reversed",$C25-$B25+1))</f>
         <v/>
       </c>
-      <c r="E25" s="64">
+      <c r="E25" s="65">
         <f>IFERROR(IF($A25="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A25,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F25" s="65">
+      <c r="F25" s="66">
         <f>IFERROR(IF($A25="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A25,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5070,17 +5076,17 @@
     </row>
     <row r="26">
       <c r="A26" s="42" t="n"/>
-      <c r="B26" s="63" t="n"/>
-      <c r="C26" s="63" t="n"/>
+      <c r="B26" s="64" t="n"/>
+      <c r="C26" s="64" t="n"/>
       <c r="D26" s="44">
         <f>IF(OR($B26="",$C26=""),"",IF($C26&lt;$B26,"⚠ dates reversed",$C26-$B26+1))</f>
         <v/>
       </c>
-      <c r="E26" s="64">
+      <c r="E26" s="65">
         <f>IFERROR(IF($A26="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A26,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F26" s="65">
+      <c r="F26" s="66">
         <f>IFERROR(IF($A26="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A26,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5092,17 +5098,17 @@
     </row>
     <row r="27">
       <c r="A27" s="42" t="n"/>
-      <c r="B27" s="63" t="n"/>
-      <c r="C27" s="63" t="n"/>
+      <c r="B27" s="64" t="n"/>
+      <c r="C27" s="64" t="n"/>
       <c r="D27" s="44">
         <f>IF(OR($B27="",$C27=""),"",IF($C27&lt;$B27,"⚠ dates reversed",$C27-$B27+1))</f>
         <v/>
       </c>
-      <c r="E27" s="64">
+      <c r="E27" s="65">
         <f>IFERROR(IF($A27="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A27,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F27" s="65">
+      <c r="F27" s="66">
         <f>IFERROR(IF($A27="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A27,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5114,17 +5120,17 @@
     </row>
     <row r="28">
       <c r="A28" s="42" t="n"/>
-      <c r="B28" s="63" t="n"/>
-      <c r="C28" s="63" t="n"/>
+      <c r="B28" s="64" t="n"/>
+      <c r="C28" s="64" t="n"/>
       <c r="D28" s="44">
         <f>IF(OR($B28="",$C28=""),"",IF($C28&lt;$B28,"⚠ dates reversed",$C28-$B28+1))</f>
         <v/>
       </c>
-      <c r="E28" s="64">
+      <c r="E28" s="65">
         <f>IFERROR(IF($A28="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A28,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F28" s="65">
+      <c r="F28" s="66">
         <f>IFERROR(IF($A28="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A28,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5136,17 +5142,17 @@
     </row>
     <row r="29">
       <c r="A29" s="42" t="n"/>
-      <c r="B29" s="63" t="n"/>
-      <c r="C29" s="63" t="n"/>
+      <c r="B29" s="64" t="n"/>
+      <c r="C29" s="64" t="n"/>
       <c r="D29" s="44">
         <f>IF(OR($B29="",$C29=""),"",IF($C29&lt;$B29,"⚠ dates reversed",$C29-$B29+1))</f>
         <v/>
       </c>
-      <c r="E29" s="64">
+      <c r="E29" s="65">
         <f>IFERROR(IF($A29="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A29,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F29" s="65">
+      <c r="F29" s="66">
         <f>IFERROR(IF($A29="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A29,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5158,17 +5164,17 @@
     </row>
     <row r="30">
       <c r="A30" s="42" t="n"/>
-      <c r="B30" s="63" t="n"/>
-      <c r="C30" s="63" t="n"/>
+      <c r="B30" s="64" t="n"/>
+      <c r="C30" s="64" t="n"/>
       <c r="D30" s="44">
         <f>IF(OR($B30="",$C30=""),"",IF($C30&lt;$B30,"⚠ dates reversed",$C30-$B30+1))</f>
         <v/>
       </c>
-      <c r="E30" s="64">
+      <c r="E30" s="65">
         <f>IFERROR(IF($A30="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A30,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F30" s="65">
+      <c r="F30" s="66">
         <f>IFERROR(IF($A30="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A30,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5180,17 +5186,17 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="n"/>
-      <c r="B31" s="63" t="n"/>
-      <c r="C31" s="63" t="n"/>
+      <c r="B31" s="64" t="n"/>
+      <c r="C31" s="64" t="n"/>
       <c r="D31" s="44">
         <f>IF(OR($B31="",$C31=""),"",IF($C31&lt;$B31,"⚠ dates reversed",$C31-$B31+1))</f>
         <v/>
       </c>
-      <c r="E31" s="64">
+      <c r="E31" s="65">
         <f>IFERROR(IF($A31="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A31,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F31" s="65">
+      <c r="F31" s="66">
         <f>IFERROR(IF($A31="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A31,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5202,17 +5208,17 @@
     </row>
     <row r="32">
       <c r="A32" s="42" t="n"/>
-      <c r="B32" s="63" t="n"/>
-      <c r="C32" s="63" t="n"/>
+      <c r="B32" s="64" t="n"/>
+      <c r="C32" s="64" t="n"/>
       <c r="D32" s="44">
         <f>IF(OR($B32="",$C32=""),"",IF($C32&lt;$B32,"⚠ dates reversed",$C32-$B32+1))</f>
         <v/>
       </c>
-      <c r="E32" s="64">
+      <c r="E32" s="65">
         <f>IFERROR(IF($A32="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A32,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F32" s="65">
+      <c r="F32" s="66">
         <f>IFERROR(IF($A32="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A32,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5224,17 +5230,17 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="n"/>
-      <c r="B33" s="63" t="n"/>
-      <c r="C33" s="63" t="n"/>
+      <c r="B33" s="64" t="n"/>
+      <c r="C33" s="64" t="n"/>
       <c r="D33" s="44">
         <f>IF(OR($B33="",$C33=""),"",IF($C33&lt;$B33,"⚠ dates reversed",$C33-$B33+1))</f>
         <v/>
       </c>
-      <c r="E33" s="64">
+      <c r="E33" s="65">
         <f>IFERROR(IF($A33="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A33,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F33" s="65">
+      <c r="F33" s="66">
         <f>IFERROR(IF($A33="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A33,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5246,17 +5252,17 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="n"/>
-      <c r="B34" s="63" t="n"/>
-      <c r="C34" s="63" t="n"/>
+      <c r="B34" s="64" t="n"/>
+      <c r="C34" s="64" t="n"/>
       <c r="D34" s="44">
         <f>IF(OR($B34="",$C34=""),"",IF($C34&lt;$B34,"⚠ dates reversed",$C34-$B34+1))</f>
         <v/>
       </c>
-      <c r="E34" s="64">
+      <c r="E34" s="65">
         <f>IFERROR(IF($A34="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A34,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F34" s="65">
+      <c r="F34" s="66">
         <f>IFERROR(IF($A34="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A34,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5268,17 +5274,17 @@
     </row>
     <row r="35">
       <c r="A35" s="33" t="n"/>
-      <c r="B35" s="66" t="n"/>
-      <c r="C35" s="66" t="n"/>
+      <c r="B35" s="67" t="n"/>
+      <c r="C35" s="67" t="n"/>
       <c r="D35" s="35">
         <f>IF(OR($B35="",$C35=""),"",IF($C35&lt;$B35,"⚠ dates reversed",$C35-$B35+1))</f>
         <v/>
       </c>
-      <c r="E35" s="67">
+      <c r="E35" s="68">
         <f>IFERROR(IF($A35="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A35,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F35" s="67">
+      <c r="F35" s="68">
         <f>IFERROR(IF($A35="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A35,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5290,17 +5296,17 @@
     </row>
     <row r="36">
       <c r="A36" s="50" t="n"/>
-      <c r="B36" s="66" t="n"/>
-      <c r="C36" s="66" t="n"/>
+      <c r="B36" s="67" t="n"/>
+      <c r="C36" s="67" t="n"/>
       <c r="D36" s="35">
         <f>IF(OR($B36="",$C36=""),"",IF($C36&lt;$B36,"⚠ dates reversed",$C36-$B36+1))</f>
         <v/>
       </c>
-      <c r="E36" s="67">
+      <c r="E36" s="68">
         <f>IFERROR(IF($A36="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A36,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F36" s="67">
+      <c r="F36" s="68">
         <f>IFERROR(IF($A36="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A36,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5312,17 +5318,17 @@
     </row>
     <row r="37">
       <c r="A37" s="33" t="n"/>
-      <c r="B37" s="66" t="n"/>
-      <c r="C37" s="66" t="n"/>
+      <c r="B37" s="67" t="n"/>
+      <c r="C37" s="67" t="n"/>
       <c r="D37" s="35">
         <f>IF(OR($B37="",$C37=""),"",IF($C37&lt;$B37,"⚠ dates reversed",$C37-$B37+1))</f>
         <v/>
       </c>
-      <c r="E37" s="67">
+      <c r="E37" s="68">
         <f>IFERROR(IF($A37="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A37,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F37" s="67">
+      <c r="F37" s="68">
         <f>IFERROR(IF($A37="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A37,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5334,17 +5340,17 @@
     </row>
     <row r="38">
       <c r="A38" s="33" t="n"/>
-      <c r="B38" s="66" t="n"/>
-      <c r="C38" s="66" t="n"/>
+      <c r="B38" s="67" t="n"/>
+      <c r="C38" s="67" t="n"/>
       <c r="D38" s="35">
         <f>IF(OR($B38="",$C38=""),"",IF($C38&lt;$B38,"⚠ dates reversed",$C38-$B38+1))</f>
         <v/>
       </c>
-      <c r="E38" s="67">
+      <c r="E38" s="68">
         <f>IFERROR(IF($A38="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A38,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="67">
+      <c r="F38" s="68">
         <f>IFERROR(IF($A38="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A38,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5356,17 +5362,17 @@
     </row>
     <row r="39">
       <c r="A39" s="33" t="n"/>
-      <c r="B39" s="66" t="n"/>
-      <c r="C39" s="66" t="n"/>
+      <c r="B39" s="67" t="n"/>
+      <c r="C39" s="67" t="n"/>
       <c r="D39" s="35">
         <f>IF(OR($B39="",$C39=""),"",IF($C39&lt;$B39,"⚠ dates reversed",$C39-$B39+1))</f>
         <v/>
       </c>
-      <c r="E39" s="67">
+      <c r="E39" s="68">
         <f>IFERROR(IF($A39="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A39,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F39" s="67">
+      <c r="F39" s="68">
         <f>IFERROR(IF($A39="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A39,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5378,17 +5384,17 @@
     </row>
     <row r="40">
       <c r="A40" s="33" t="n"/>
-      <c r="B40" s="66" t="n"/>
-      <c r="C40" s="66" t="n"/>
+      <c r="B40" s="67" t="n"/>
+      <c r="C40" s="67" t="n"/>
       <c r="D40" s="35">
         <f>IF(OR($B40="",$C40=""),"",IF($C40&lt;$B40,"⚠ dates reversed",$C40-$B40+1))</f>
         <v/>
       </c>
-      <c r="E40" s="67">
+      <c r="E40" s="68">
         <f>IFERROR(IF($A40="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A40,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F40" s="67">
+      <c r="F40" s="68">
         <f>IFERROR(IF($A40="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A40,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5400,17 +5406,17 @@
     </row>
     <row r="41">
       <c r="A41" s="33" t="n"/>
-      <c r="B41" s="66" t="n"/>
-      <c r="C41" s="66" t="n"/>
+      <c r="B41" s="67" t="n"/>
+      <c r="C41" s="67" t="n"/>
       <c r="D41" s="35">
         <f>IF(OR($B41="",$C41=""),"",IF($C41&lt;$B41,"⚠ dates reversed",$C41-$B41+1))</f>
         <v/>
       </c>
-      <c r="E41" s="67">
+      <c r="E41" s="68">
         <f>IFERROR(IF($A41="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A41,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="67">
+      <c r="F41" s="68">
         <f>IFERROR(IF($A41="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A41,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5422,17 +5428,17 @@
     </row>
     <row r="42">
       <c r="A42" s="33" t="n"/>
-      <c r="B42" s="66" t="n"/>
-      <c r="C42" s="66" t="n"/>
+      <c r="B42" s="67" t="n"/>
+      <c r="C42" s="67" t="n"/>
       <c r="D42" s="35">
         <f>IF(OR($B42="",$C42=""),"",IF($C42&lt;$B42,"⚠ dates reversed",$C42-$B42+1))</f>
         <v/>
       </c>
-      <c r="E42" s="67">
+      <c r="E42" s="68">
         <f>IFERROR(IF($A42="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A42,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F42" s="67">
+      <c r="F42" s="68">
         <f>IFERROR(IF($A42="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A42,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5444,17 +5450,17 @@
     </row>
     <row r="43">
       <c r="A43" s="33" t="n"/>
-      <c r="B43" s="66" t="n"/>
-      <c r="C43" s="66" t="n"/>
+      <c r="B43" s="67" t="n"/>
+      <c r="C43" s="67" t="n"/>
       <c r="D43" s="35">
         <f>IF(OR($B43="",$C43=""),"",IF($C43&lt;$B43,"⚠ dates reversed",$C43-$B43+1))</f>
         <v/>
       </c>
-      <c r="E43" s="67">
+      <c r="E43" s="68">
         <f>IFERROR(IF($A43="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A43,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F43" s="67">
+      <c r="F43" s="68">
         <f>IFERROR(IF($A43="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A43,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5466,17 +5472,17 @@
     </row>
     <row r="44">
       <c r="A44" s="33" t="n"/>
-      <c r="B44" s="66" t="n"/>
-      <c r="C44" s="66" t="n"/>
+      <c r="B44" s="67" t="n"/>
+      <c r="C44" s="67" t="n"/>
       <c r="D44" s="35">
         <f>IF(OR($B44="",$C44=""),"",IF($C44&lt;$B44,"⚠ dates reversed",$C44-$B44+1))</f>
         <v/>
       </c>
-      <c r="E44" s="67">
+      <c r="E44" s="68">
         <f>IFERROR(IF($A44="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A44,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F44" s="67">
+      <c r="F44" s="68">
         <f>IFERROR(IF($A44="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A44,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5488,17 +5494,17 @@
     </row>
     <row r="45">
       <c r="A45" s="33" t="n"/>
-      <c r="B45" s="66" t="n"/>
-      <c r="C45" s="66" t="n"/>
+      <c r="B45" s="67" t="n"/>
+      <c r="C45" s="67" t="n"/>
       <c r="D45" s="35">
         <f>IF(OR($B45="",$C45=""),"",IF($C45&lt;$B45,"⚠ dates reversed",$C45-$B45+1))</f>
         <v/>
       </c>
-      <c r="E45" s="67">
+      <c r="E45" s="68">
         <f>IFERROR(IF($A45="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A45,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F45" s="67">
+      <c r="F45" s="68">
         <f>IFERROR(IF($A45="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A45,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5510,17 +5516,17 @@
     </row>
     <row r="46">
       <c r="A46" s="33" t="n"/>
-      <c r="B46" s="66" t="n"/>
-      <c r="C46" s="66" t="n"/>
+      <c r="B46" s="67" t="n"/>
+      <c r="C46" s="67" t="n"/>
       <c r="D46" s="35">
         <f>IF(OR($B46="",$C46=""),"",IF($C46&lt;$B46,"⚠ dates reversed",$C46-$B46+1))</f>
         <v/>
       </c>
-      <c r="E46" s="67">
+      <c r="E46" s="68">
         <f>IFERROR(IF($A46="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A46,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F46" s="67">
+      <c r="F46" s="68">
         <f>IFERROR(IF($A46="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A46,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5532,17 +5538,17 @@
     </row>
     <row r="47">
       <c r="A47" s="33" t="n"/>
-      <c r="B47" s="66" t="n"/>
-      <c r="C47" s="66" t="n"/>
+      <c r="B47" s="67" t="n"/>
+      <c r="C47" s="67" t="n"/>
       <c r="D47" s="35">
         <f>IF(OR($B47="",$C47=""),"",IF($C47&lt;$B47,"⚠ dates reversed",$C47-$B47+1))</f>
         <v/>
       </c>
-      <c r="E47" s="67">
+      <c r="E47" s="68">
         <f>IFERROR(IF($A47="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A47,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F47" s="67">
+      <c r="F47" s="68">
         <f>IFERROR(IF($A47="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A47,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5554,17 +5560,17 @@
     </row>
     <row r="48">
       <c r="A48" s="33" t="n"/>
-      <c r="B48" s="66" t="n"/>
-      <c r="C48" s="66" t="n"/>
+      <c r="B48" s="67" t="n"/>
+      <c r="C48" s="67" t="n"/>
       <c r="D48" s="35">
         <f>IF(OR($B48="",$C48=""),"",IF($C48&lt;$B48,"⚠ dates reversed",$C48-$B48+1))</f>
         <v/>
       </c>
-      <c r="E48" s="67">
+      <c r="E48" s="68">
         <f>IFERROR(IF($A48="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A48,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F48" s="67">
+      <c r="F48" s="68">
         <f>IFERROR(IF($A48="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A48,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5576,17 +5582,17 @@
     </row>
     <row r="49">
       <c r="A49" s="33" t="n"/>
-      <c r="B49" s="66" t="n"/>
-      <c r="C49" s="66" t="n"/>
+      <c r="B49" s="67" t="n"/>
+      <c r="C49" s="67" t="n"/>
       <c r="D49" s="35">
         <f>IF(OR($B49="",$C49=""),"",IF($C49&lt;$B49,"⚠ dates reversed",$C49-$B49+1))</f>
         <v/>
       </c>
-      <c r="E49" s="67">
+      <c r="E49" s="68">
         <f>IFERROR(IF($A49="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A49,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="67">
+      <c r="F49" s="68">
         <f>IFERROR(IF($A49="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A49,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5598,17 +5604,17 @@
     </row>
     <row r="50">
       <c r="A50" s="33" t="n"/>
-      <c r="B50" s="66" t="n"/>
-      <c r="C50" s="66" t="n"/>
+      <c r="B50" s="67" t="n"/>
+      <c r="C50" s="67" t="n"/>
       <c r="D50" s="35">
         <f>IF(OR($B50="",$C50=""),"",IF($C50&lt;$B50,"⚠ dates reversed",$C50-$B50+1))</f>
         <v/>
       </c>
-      <c r="E50" s="67">
+      <c r="E50" s="68">
         <f>IFERROR(IF($A50="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A50,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F50" s="67">
+      <c r="F50" s="68">
         <f>IFERROR(IF($A50="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A50,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5620,17 +5626,17 @@
     </row>
     <row r="51">
       <c r="A51" s="33" t="n"/>
-      <c r="B51" s="66" t="n"/>
-      <c r="C51" s="66" t="n"/>
+      <c r="B51" s="67" t="n"/>
+      <c r="C51" s="67" t="n"/>
       <c r="D51" s="35">
         <f>IF(OR($B51="",$C51=""),"",IF($C51&lt;$B51,"⚠ dates reversed",$C51-$B51+1))</f>
         <v/>
       </c>
-      <c r="E51" s="67">
+      <c r="E51" s="68">
         <f>IFERROR(IF($A51="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A51,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F51" s="67">
+      <c r="F51" s="68">
         <f>IFERROR(IF($A51="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A51,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5642,17 +5648,17 @@
     </row>
     <row r="52">
       <c r="A52" s="33" t="n"/>
-      <c r="B52" s="66" t="n"/>
-      <c r="C52" s="66" t="n"/>
+      <c r="B52" s="67" t="n"/>
+      <c r="C52" s="67" t="n"/>
       <c r="D52" s="35">
         <f>IF(OR($B52="",$C52=""),"",IF($C52&lt;$B52,"⚠ dates reversed",$C52-$B52+1))</f>
         <v/>
       </c>
-      <c r="E52" s="67">
+      <c r="E52" s="68">
         <f>IFERROR(IF($A52="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A52,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F52" s="67">
+      <c r="F52" s="68">
         <f>IFERROR(IF($A52="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A52,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5664,17 +5670,17 @@
     </row>
     <row r="53">
       <c r="A53" s="33" t="n"/>
-      <c r="B53" s="66" t="n"/>
-      <c r="C53" s="66" t="n"/>
+      <c r="B53" s="67" t="n"/>
+      <c r="C53" s="67" t="n"/>
       <c r="D53" s="35">
         <f>IF(OR($B53="",$C53=""),"",IF($C53&lt;$B53,"⚠ dates reversed",$C53-$B53+1))</f>
         <v/>
       </c>
-      <c r="E53" s="67">
+      <c r="E53" s="68">
         <f>IFERROR(IF($A53="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A53,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F53" s="67">
+      <c r="F53" s="68">
         <f>IFERROR(IF($A53="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A53,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5686,17 +5692,17 @@
     </row>
     <row r="54">
       <c r="A54" s="33" t="n"/>
-      <c r="B54" s="66" t="n"/>
-      <c r="C54" s="66" t="n"/>
+      <c r="B54" s="67" t="n"/>
+      <c r="C54" s="67" t="n"/>
       <c r="D54" s="35">
         <f>IF(OR($B54="",$C54=""),"",IF($C54&lt;$B54,"⚠ dates reversed",$C54-$B54+1))</f>
         <v/>
       </c>
-      <c r="E54" s="67">
+      <c r="E54" s="68">
         <f>IFERROR(IF($A54="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A54,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F54" s="67">
+      <c r="F54" s="68">
         <f>IFERROR(IF($A54="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A54,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5708,17 +5714,17 @@
     </row>
     <row r="55">
       <c r="A55" s="33" t="n"/>
-      <c r="B55" s="66" t="n"/>
-      <c r="C55" s="66" t="n"/>
+      <c r="B55" s="67" t="n"/>
+      <c r="C55" s="67" t="n"/>
       <c r="D55" s="35">
         <f>IF(OR($B55="",$C55=""),"",IF($C55&lt;$B55,"⚠ dates reversed",$C55-$B55+1))</f>
         <v/>
       </c>
-      <c r="E55" s="67">
+      <c r="E55" s="68">
         <f>IFERROR(IF($A55="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A55,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F55" s="67">
+      <c r="F55" s="68">
         <f>IFERROR(IF($A55="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A55,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5730,17 +5736,17 @@
     </row>
     <row r="56">
       <c r="A56" s="33" t="n"/>
-      <c r="B56" s="66" t="n"/>
-      <c r="C56" s="66" t="n"/>
+      <c r="B56" s="67" t="n"/>
+      <c r="C56" s="67" t="n"/>
       <c r="D56" s="35">
         <f>IF(OR($B56="",$C56=""),"",IF($C56&lt;$B56,"⚠ dates reversed",$C56-$B56+1))</f>
         <v/>
       </c>
-      <c r="E56" s="67">
+      <c r="E56" s="68">
         <f>IFERROR(IF($A56="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A56,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F56" s="67">
+      <c r="F56" s="68">
         <f>IFERROR(IF($A56="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A56,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5752,17 +5758,17 @@
     </row>
     <row r="57">
       <c r="A57" s="33" t="n"/>
-      <c r="B57" s="66" t="n"/>
-      <c r="C57" s="66" t="n"/>
+      <c r="B57" s="67" t="n"/>
+      <c r="C57" s="67" t="n"/>
       <c r="D57" s="35">
         <f>IF(OR($B57="",$C57=""),"",IF($C57&lt;$B57,"⚠ dates reversed",$C57-$B57+1))</f>
         <v/>
       </c>
-      <c r="E57" s="67">
+      <c r="E57" s="68">
         <f>IFERROR(IF($A57="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A57,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F57" s="67">
+      <c r="F57" s="68">
         <f>IFERROR(IF($A57="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A57,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5774,17 +5780,17 @@
     </row>
     <row r="58">
       <c r="A58" s="33" t="n"/>
-      <c r="B58" s="66" t="n"/>
-      <c r="C58" s="66" t="n"/>
+      <c r="B58" s="67" t="n"/>
+      <c r="C58" s="67" t="n"/>
       <c r="D58" s="35">
         <f>IF(OR($B58="",$C58=""),"",IF($C58&lt;$B58,"⚠ dates reversed",$C58-$B58+1))</f>
         <v/>
       </c>
-      <c r="E58" s="67">
+      <c r="E58" s="68">
         <f>IFERROR(IF($A58="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A58,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F58" s="67">
+      <c r="F58" s="68">
         <f>IFERROR(IF($A58="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A58,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5796,17 +5802,17 @@
     </row>
     <row r="59">
       <c r="A59" s="33" t="n"/>
-      <c r="B59" s="66" t="n"/>
-      <c r="C59" s="66" t="n"/>
+      <c r="B59" s="67" t="n"/>
+      <c r="C59" s="67" t="n"/>
       <c r="D59" s="35">
         <f>IF(OR($B59="",$C59=""),"",IF($C59&lt;$B59,"⚠ dates reversed",$C59-$B59+1))</f>
         <v/>
       </c>
-      <c r="E59" s="67">
+      <c r="E59" s="68">
         <f>IFERROR(IF($A59="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A59,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F59" s="67">
+      <c r="F59" s="68">
         <f>IFERROR(IF($A59="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A59,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5818,17 +5824,17 @@
     </row>
     <row r="60">
       <c r="A60" s="33" t="n"/>
-      <c r="B60" s="66" t="n"/>
-      <c r="C60" s="66" t="n"/>
+      <c r="B60" s="67" t="n"/>
+      <c r="C60" s="67" t="n"/>
       <c r="D60" s="35">
         <f>IF(OR($B60="",$C60=""),"",IF($C60&lt;$B60,"⚠ dates reversed",$C60-$B60+1))</f>
         <v/>
       </c>
-      <c r="E60" s="67">
+      <c r="E60" s="68">
         <f>IFERROR(IF($A60="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A60,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F60" s="67">
+      <c r="F60" s="68">
         <f>IFERROR(IF($A60="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A60,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5840,17 +5846,17 @@
     </row>
     <row r="61">
       <c r="A61" s="33" t="n"/>
-      <c r="B61" s="66" t="n"/>
-      <c r="C61" s="66" t="n"/>
+      <c r="B61" s="67" t="n"/>
+      <c r="C61" s="67" t="n"/>
       <c r="D61" s="35">
         <f>IF(OR($B61="",$C61=""),"",IF($C61&lt;$B61,"⚠ dates reversed",$C61-$B61+1))</f>
         <v/>
       </c>
-      <c r="E61" s="67">
+      <c r="E61" s="68">
         <f>IFERROR(IF($A61="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A61,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F61" s="67">
+      <c r="F61" s="68">
         <f>IFERROR(IF($A61="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A61,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5862,17 +5868,17 @@
     </row>
     <row r="62">
       <c r="A62" s="33" t="n"/>
-      <c r="B62" s="66" t="n"/>
-      <c r="C62" s="66" t="n"/>
+      <c r="B62" s="67" t="n"/>
+      <c r="C62" s="67" t="n"/>
       <c r="D62" s="35">
         <f>IF(OR($B62="",$C62=""),"",IF($C62&lt;$B62,"⚠ dates reversed",$C62-$B62+1))</f>
         <v/>
       </c>
-      <c r="E62" s="67">
+      <c r="E62" s="68">
         <f>IFERROR(IF($A62="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A62,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F62" s="67">
+      <c r="F62" s="68">
         <f>IFERROR(IF($A62="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A62,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5884,17 +5890,17 @@
     </row>
     <row r="63">
       <c r="A63" s="33" t="n"/>
-      <c r="B63" s="66" t="n"/>
-      <c r="C63" s="66" t="n"/>
+      <c r="B63" s="67" t="n"/>
+      <c r="C63" s="67" t="n"/>
       <c r="D63" s="35">
         <f>IF(OR($B63="",$C63=""),"",IF($C63&lt;$B63,"⚠ dates reversed",$C63-$B63+1))</f>
         <v/>
       </c>
-      <c r="E63" s="67">
+      <c r="E63" s="68">
         <f>IFERROR(IF($A63="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A63,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F63" s="67">
+      <c r="F63" s="68">
         <f>IFERROR(IF($A63="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A63,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5906,17 +5912,17 @@
     </row>
     <row r="64">
       <c r="A64" s="33" t="n"/>
-      <c r="B64" s="66" t="n"/>
-      <c r="C64" s="66" t="n"/>
+      <c r="B64" s="67" t="n"/>
+      <c r="C64" s="67" t="n"/>
       <c r="D64" s="35">
         <f>IF(OR($B64="",$C64=""),"",IF($C64&lt;$B64,"⚠ dates reversed",$C64-$B64+1))</f>
         <v/>
       </c>
-      <c r="E64" s="67">
+      <c r="E64" s="68">
         <f>IFERROR(IF($A64="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A64,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F64" s="67">
+      <c r="F64" s="68">
         <f>IFERROR(IF($A64="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A64,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5928,17 +5934,17 @@
     </row>
     <row r="65">
       <c r="A65" s="33" t="n"/>
-      <c r="B65" s="66" t="n"/>
-      <c r="C65" s="66" t="n"/>
+      <c r="B65" s="67" t="n"/>
+      <c r="C65" s="67" t="n"/>
       <c r="D65" s="35">
         <f>IF(OR($B65="",$C65=""),"",IF($C65&lt;$B65,"⚠ dates reversed",$C65-$B65+1))</f>
         <v/>
       </c>
-      <c r="E65" s="67">
+      <c r="E65" s="68">
         <f>IFERROR(IF($A65="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A65,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F65" s="67">
+      <c r="F65" s="68">
         <f>IFERROR(IF($A65="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A65,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5950,17 +5956,17 @@
     </row>
     <row r="66">
       <c r="A66" s="33" t="n"/>
-      <c r="B66" s="66" t="n"/>
-      <c r="C66" s="66" t="n"/>
+      <c r="B66" s="67" t="n"/>
+      <c r="C66" s="67" t="n"/>
       <c r="D66" s="35">
         <f>IF(OR($B66="",$C66=""),"",IF($C66&lt;$B66,"⚠ dates reversed",$C66-$B66+1))</f>
         <v/>
       </c>
-      <c r="E66" s="67">
+      <c r="E66" s="68">
         <f>IFERROR(IF($A66="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A66,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F66" s="67">
+      <c r="F66" s="68">
         <f>IFERROR(IF($A66="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A66,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5972,17 +5978,17 @@
     </row>
     <row r="67">
       <c r="A67" s="33" t="n"/>
-      <c r="B67" s="66" t="n"/>
-      <c r="C67" s="66" t="n"/>
+      <c r="B67" s="67" t="n"/>
+      <c r="C67" s="67" t="n"/>
       <c r="D67" s="35">
         <f>IF(OR($B67="",$C67=""),"",IF($C67&lt;$B67,"⚠ dates reversed",$C67-$B67+1))</f>
         <v/>
       </c>
-      <c r="E67" s="67">
+      <c r="E67" s="68">
         <f>IFERROR(IF($A67="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A67,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F67" s="67">
+      <c r="F67" s="68">
         <f>IFERROR(IF($A67="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A67,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -5994,17 +6000,17 @@
     </row>
     <row r="68">
       <c r="A68" s="33" t="n"/>
-      <c r="B68" s="66" t="n"/>
-      <c r="C68" s="66" t="n"/>
+      <c r="B68" s="67" t="n"/>
+      <c r="C68" s="67" t="n"/>
       <c r="D68" s="35">
         <f>IF(OR($B68="",$C68=""),"",IF($C68&lt;$B68,"⚠ dates reversed",$C68-$B68+1))</f>
         <v/>
       </c>
-      <c r="E68" s="67">
+      <c r="E68" s="68">
         <f>IFERROR(IF($A68="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A68,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F68" s="67">
+      <c r="F68" s="68">
         <f>IFERROR(IF($A68="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A68,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6016,17 +6022,17 @@
     </row>
     <row r="69">
       <c r="A69" s="33" t="n"/>
-      <c r="B69" s="66" t="n"/>
-      <c r="C69" s="66" t="n"/>
+      <c r="B69" s="67" t="n"/>
+      <c r="C69" s="67" t="n"/>
       <c r="D69" s="35">
         <f>IF(OR($B69="",$C69=""),"",IF($C69&lt;$B69,"⚠ dates reversed",$C69-$B69+1))</f>
         <v/>
       </c>
-      <c r="E69" s="67">
+      <c r="E69" s="68">
         <f>IFERROR(IF($A69="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A69,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F69" s="67">
+      <c r="F69" s="68">
         <f>IFERROR(IF($A69="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A69,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6038,17 +6044,17 @@
     </row>
     <row r="70">
       <c r="A70" s="33" t="n"/>
-      <c r="B70" s="66" t="n"/>
-      <c r="C70" s="66" t="n"/>
+      <c r="B70" s="67" t="n"/>
+      <c r="C70" s="67" t="n"/>
       <c r="D70" s="35">
         <f>IF(OR($B70="",$C70=""),"",IF($C70&lt;$B70,"⚠ dates reversed",$C70-$B70+1))</f>
         <v/>
       </c>
-      <c r="E70" s="67">
+      <c r="E70" s="68">
         <f>IFERROR(IF($A70="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A70,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F70" s="67">
+      <c r="F70" s="68">
         <f>IFERROR(IF($A70="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A70,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6060,17 +6066,17 @@
     </row>
     <row r="71">
       <c r="A71" s="33" t="n"/>
-      <c r="B71" s="66" t="n"/>
-      <c r="C71" s="66" t="n"/>
+      <c r="B71" s="67" t="n"/>
+      <c r="C71" s="67" t="n"/>
       <c r="D71" s="35">
         <f>IF(OR($B71="",$C71=""),"",IF($C71&lt;$B71,"⚠ dates reversed",$C71-$B71+1))</f>
         <v/>
       </c>
-      <c r="E71" s="67">
+      <c r="E71" s="68">
         <f>IFERROR(IF($A71="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A71,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F71" s="67">
+      <c r="F71" s="68">
         <f>IFERROR(IF($A71="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A71,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6082,17 +6088,17 @@
     </row>
     <row r="72">
       <c r="A72" s="33" t="n"/>
-      <c r="B72" s="66" t="n"/>
-      <c r="C72" s="66" t="n"/>
+      <c r="B72" s="67" t="n"/>
+      <c r="C72" s="67" t="n"/>
       <c r="D72" s="35">
         <f>IF(OR($B72="",$C72=""),"",IF($C72&lt;$B72,"⚠ dates reversed",$C72-$B72+1))</f>
         <v/>
       </c>
-      <c r="E72" s="67">
+      <c r="E72" s="68">
         <f>IFERROR(IF($A72="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A72,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F72" s="67">
+      <c r="F72" s="68">
         <f>IFERROR(IF($A72="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A72,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6104,17 +6110,17 @@
     </row>
     <row r="73">
       <c r="A73" s="33" t="n"/>
-      <c r="B73" s="66" t="n"/>
-      <c r="C73" s="66" t="n"/>
+      <c r="B73" s="67" t="n"/>
+      <c r="C73" s="67" t="n"/>
       <c r="D73" s="35">
         <f>IF(OR($B73="",$C73=""),"",IF($C73&lt;$B73,"⚠ dates reversed",$C73-$B73+1))</f>
         <v/>
       </c>
-      <c r="E73" s="67">
+      <c r="E73" s="68">
         <f>IFERROR(IF($A73="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A73,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F73" s="67">
+      <c r="F73" s="68">
         <f>IFERROR(IF($A73="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A73,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6126,17 +6132,17 @@
     </row>
     <row r="74">
       <c r="A74" s="33" t="n"/>
-      <c r="B74" s="66" t="n"/>
-      <c r="C74" s="66" t="n"/>
+      <c r="B74" s="67" t="n"/>
+      <c r="C74" s="67" t="n"/>
       <c r="D74" s="35">
         <f>IF(OR($B74="",$C74=""),"",IF($C74&lt;$B74,"⚠ dates reversed",$C74-$B74+1))</f>
         <v/>
       </c>
-      <c r="E74" s="67">
+      <c r="E74" s="68">
         <f>IFERROR(IF($A74="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A74,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F74" s="67">
+      <c r="F74" s="68">
         <f>IFERROR(IF($A74="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A74,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6148,17 +6154,17 @@
     </row>
     <row r="75">
       <c r="A75" s="33" t="n"/>
-      <c r="B75" s="66" t="n"/>
-      <c r="C75" s="66" t="n"/>
+      <c r="B75" s="67" t="n"/>
+      <c r="C75" s="67" t="n"/>
       <c r="D75" s="35">
         <f>IF(OR($B75="",$C75=""),"",IF($C75&lt;$B75,"⚠ dates reversed",$C75-$B75+1))</f>
         <v/>
       </c>
-      <c r="E75" s="67">
+      <c r="E75" s="68">
         <f>IFERROR(IF($A75="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A75,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F75" s="67">
+      <c r="F75" s="68">
         <f>IFERROR(IF($A75="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A75,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6170,17 +6176,17 @@
     </row>
     <row r="76">
       <c r="A76" s="33" t="n"/>
-      <c r="B76" s="66" t="n"/>
-      <c r="C76" s="66" t="n"/>
+      <c r="B76" s="67" t="n"/>
+      <c r="C76" s="67" t="n"/>
       <c r="D76" s="35">
         <f>IF(OR($B76="",$C76=""),"",IF($C76&lt;$B76,"⚠ dates reversed",$C76-$B76+1))</f>
         <v/>
       </c>
-      <c r="E76" s="67">
+      <c r="E76" s="68">
         <f>IFERROR(IF($A76="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A76,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F76" s="67">
+      <c r="F76" s="68">
         <f>IFERROR(IF($A76="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A76,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6192,17 +6198,17 @@
     </row>
     <row r="77">
       <c r="A77" s="33" t="n"/>
-      <c r="B77" s="66" t="n"/>
-      <c r="C77" s="66" t="n"/>
+      <c r="B77" s="67" t="n"/>
+      <c r="C77" s="67" t="n"/>
       <c r="D77" s="35">
         <f>IF(OR($B77="",$C77=""),"",IF($C77&lt;$B77,"⚠ dates reversed",$C77-$B77+1))</f>
         <v/>
       </c>
-      <c r="E77" s="67">
+      <c r="E77" s="68">
         <f>IFERROR(IF($A77="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A77,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F77" s="67">
+      <c r="F77" s="68">
         <f>IFERROR(IF($A77="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A77,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6214,17 +6220,17 @@
     </row>
     <row r="78">
       <c r="A78" s="33" t="n"/>
-      <c r="B78" s="66" t="n"/>
-      <c r="C78" s="66" t="n"/>
+      <c r="B78" s="67" t="n"/>
+      <c r="C78" s="67" t="n"/>
       <c r="D78" s="35">
         <f>IF(OR($B78="",$C78=""),"",IF($C78&lt;$B78,"⚠ dates reversed",$C78-$B78+1))</f>
         <v/>
       </c>
-      <c r="E78" s="67">
+      <c r="E78" s="68">
         <f>IFERROR(IF($A78="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A78,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F78" s="67">
+      <c r="F78" s="68">
         <f>IFERROR(IF($A78="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A78,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6236,17 +6242,17 @@
     </row>
     <row r="79">
       <c r="A79" s="33" t="n"/>
-      <c r="B79" s="66" t="n"/>
-      <c r="C79" s="66" t="n"/>
+      <c r="B79" s="67" t="n"/>
+      <c r="C79" s="67" t="n"/>
       <c r="D79" s="35">
         <f>IF(OR($B79="",$C79=""),"",IF($C79&lt;$B79,"⚠ dates reversed",$C79-$B79+1))</f>
         <v/>
       </c>
-      <c r="E79" s="67">
+      <c r="E79" s="68">
         <f>IFERROR(IF($A79="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A79,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F79" s="67">
+      <c r="F79" s="68">
         <f>IFERROR(IF($A79="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A79,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6258,17 +6264,17 @@
     </row>
     <row r="80">
       <c r="A80" s="33" t="n"/>
-      <c r="B80" s="66" t="n"/>
-      <c r="C80" s="66" t="n"/>
+      <c r="B80" s="67" t="n"/>
+      <c r="C80" s="67" t="n"/>
       <c r="D80" s="35">
         <f>IF(OR($B80="",$C80=""),"",IF($C80&lt;$B80,"⚠ dates reversed",$C80-$B80+1))</f>
         <v/>
       </c>
-      <c r="E80" s="67">
+      <c r="E80" s="68">
         <f>IFERROR(IF($A80="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A80,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F80" s="67">
+      <c r="F80" s="68">
         <f>IFERROR(IF($A80="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A80,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6280,17 +6286,17 @@
     </row>
     <row r="81">
       <c r="A81" s="33" t="n"/>
-      <c r="B81" s="66" t="n"/>
-      <c r="C81" s="66" t="n"/>
+      <c r="B81" s="67" t="n"/>
+      <c r="C81" s="67" t="n"/>
       <c r="D81" s="35">
         <f>IF(OR($B81="",$C81=""),"",IF($C81&lt;$B81,"⚠ dates reversed",$C81-$B81+1))</f>
         <v/>
       </c>
-      <c r="E81" s="67">
+      <c r="E81" s="68">
         <f>IFERROR(IF($A81="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A81,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F81" s="67">
+      <c r="F81" s="68">
         <f>IFERROR(IF($A81="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A81,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6302,17 +6308,17 @@
     </row>
     <row r="82">
       <c r="A82" s="33" t="n"/>
-      <c r="B82" s="66" t="n"/>
-      <c r="C82" s="66" t="n"/>
+      <c r="B82" s="67" t="n"/>
+      <c r="C82" s="67" t="n"/>
       <c r="D82" s="35">
         <f>IF(OR($B82="",$C82=""),"",IF($C82&lt;$B82,"⚠ dates reversed",$C82-$B82+1))</f>
         <v/>
       </c>
-      <c r="E82" s="67">
+      <c r="E82" s="68">
         <f>IFERROR(IF($A82="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A82,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F82" s="67">
+      <c r="F82" s="68">
         <f>IFERROR(IF($A82="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A82,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6324,17 +6330,17 @@
     </row>
     <row r="83">
       <c r="A83" s="33" t="n"/>
-      <c r="B83" s="66" t="n"/>
-      <c r="C83" s="66" t="n"/>
+      <c r="B83" s="67" t="n"/>
+      <c r="C83" s="67" t="n"/>
       <c r="D83" s="35">
         <f>IF(OR($B83="",$C83=""),"",IF($C83&lt;$B83,"⚠ dates reversed",$C83-$B83+1))</f>
         <v/>
       </c>
-      <c r="E83" s="67">
+      <c r="E83" s="68">
         <f>IFERROR(IF($A83="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A83,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F83" s="67">
+      <c r="F83" s="68">
         <f>IFERROR(IF($A83="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A83,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6346,17 +6352,17 @@
     </row>
     <row r="84">
       <c r="A84" s="33" t="n"/>
-      <c r="B84" s="66" t="n"/>
-      <c r="C84" s="66" t="n"/>
+      <c r="B84" s="67" t="n"/>
+      <c r="C84" s="67" t="n"/>
       <c r="D84" s="35">
         <f>IF(OR($B84="",$C84=""),"",IF($C84&lt;$B84,"⚠ dates reversed",$C84-$B84+1))</f>
         <v/>
       </c>
-      <c r="E84" s="67">
+      <c r="E84" s="68">
         <f>IFERROR(IF($A84="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A84,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F84" s="67">
+      <c r="F84" s="68">
         <f>IFERROR(IF($A84="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A84,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6368,17 +6374,17 @@
     </row>
     <row r="85">
       <c r="A85" s="33" t="n"/>
-      <c r="B85" s="66" t="n"/>
-      <c r="C85" s="66" t="n"/>
+      <c r="B85" s="67" t="n"/>
+      <c r="C85" s="67" t="n"/>
       <c r="D85" s="35">
         <f>IF(OR($B85="",$C85=""),"",IF($C85&lt;$B85,"⚠ dates reversed",$C85-$B85+1))</f>
         <v/>
       </c>
-      <c r="E85" s="67">
+      <c r="E85" s="68">
         <f>IFERROR(IF($A85="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A85,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F85" s="67">
+      <c r="F85" s="68">
         <f>IFERROR(IF($A85="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A85,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6390,17 +6396,17 @@
     </row>
     <row r="86">
       <c r="A86" s="33" t="n"/>
-      <c r="B86" s="66" t="n"/>
-      <c r="C86" s="66" t="n"/>
+      <c r="B86" s="67" t="n"/>
+      <c r="C86" s="67" t="n"/>
       <c r="D86" s="35">
         <f>IF(OR($B86="",$C86=""),"",IF($C86&lt;$B86,"⚠ dates reversed",$C86-$B86+1))</f>
         <v/>
       </c>
-      <c r="E86" s="67">
+      <c r="E86" s="68">
         <f>IFERROR(IF($A86="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A86,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F86" s="67">
+      <c r="F86" s="68">
         <f>IFERROR(IF($A86="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A86,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6412,17 +6418,17 @@
     </row>
     <row r="87">
       <c r="A87" s="33" t="n"/>
-      <c r="B87" s="66" t="n"/>
-      <c r="C87" s="66" t="n"/>
+      <c r="B87" s="67" t="n"/>
+      <c r="C87" s="67" t="n"/>
       <c r="D87" s="35">
         <f>IF(OR($B87="",$C87=""),"",IF($C87&lt;$B87,"⚠ dates reversed",$C87-$B87+1))</f>
         <v/>
       </c>
-      <c r="E87" s="67">
+      <c r="E87" s="68">
         <f>IFERROR(IF($A87="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A87,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F87" s="67">
+      <c r="F87" s="68">
         <f>IFERROR(IF($A87="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A87,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6434,17 +6440,17 @@
     </row>
     <row r="88">
       <c r="A88" s="33" t="n"/>
-      <c r="B88" s="66" t="n"/>
-      <c r="C88" s="66" t="n"/>
+      <c r="B88" s="67" t="n"/>
+      <c r="C88" s="67" t="n"/>
       <c r="D88" s="35">
         <f>IF(OR($B88="",$C88=""),"",IF($C88&lt;$B88,"⚠ dates reversed",$C88-$B88+1))</f>
         <v/>
       </c>
-      <c r="E88" s="67">
+      <c r="E88" s="68">
         <f>IFERROR(IF($A88="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A88,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F88" s="67">
+      <c r="F88" s="68">
         <f>IFERROR(IF($A88="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A88,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6456,17 +6462,17 @@
     </row>
     <row r="89">
       <c r="A89" s="33" t="n"/>
-      <c r="B89" s="66" t="n"/>
-      <c r="C89" s="66" t="n"/>
+      <c r="B89" s="67" t="n"/>
+      <c r="C89" s="67" t="n"/>
       <c r="D89" s="35">
         <f>IF(OR($B89="",$C89=""),"",IF($C89&lt;$B89,"⚠ dates reversed",$C89-$B89+1))</f>
         <v/>
       </c>
-      <c r="E89" s="67">
+      <c r="E89" s="68">
         <f>IFERROR(IF($A89="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A89,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F89" s="67">
+      <c r="F89" s="68">
         <f>IFERROR(IF($A89="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A89,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6478,17 +6484,17 @@
     </row>
     <row r="90">
       <c r="A90" s="33" t="n"/>
-      <c r="B90" s="66" t="n"/>
-      <c r="C90" s="66" t="n"/>
+      <c r="B90" s="67" t="n"/>
+      <c r="C90" s="67" t="n"/>
       <c r="D90" s="35">
         <f>IF(OR($B90="",$C90=""),"",IF($C90&lt;$B90,"⚠ dates reversed",$C90-$B90+1))</f>
         <v/>
       </c>
-      <c r="E90" s="67">
+      <c r="E90" s="68">
         <f>IFERROR(IF($A90="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A90,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F90" s="67">
+      <c r="F90" s="68">
         <f>IFERROR(IF($A90="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A90,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6500,17 +6506,17 @@
     </row>
     <row r="91">
       <c r="A91" s="33" t="n"/>
-      <c r="B91" s="66" t="n"/>
-      <c r="C91" s="66" t="n"/>
+      <c r="B91" s="67" t="n"/>
+      <c r="C91" s="67" t="n"/>
       <c r="D91" s="35">
         <f>IF(OR($B91="",$C91=""),"",IF($C91&lt;$B91,"⚠ dates reversed",$C91-$B91+1))</f>
         <v/>
       </c>
-      <c r="E91" s="67">
+      <c r="E91" s="68">
         <f>IFERROR(IF($A91="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A91,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F91" s="67">
+      <c r="F91" s="68">
         <f>IFERROR(IF($A91="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A91,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6522,17 +6528,17 @@
     </row>
     <row r="92">
       <c r="A92" s="33" t="n"/>
-      <c r="B92" s="66" t="n"/>
-      <c r="C92" s="66" t="n"/>
+      <c r="B92" s="67" t="n"/>
+      <c r="C92" s="67" t="n"/>
       <c r="D92" s="35">
         <f>IF(OR($B92="",$C92=""),"",IF($C92&lt;$B92,"⚠ dates reversed",$C92-$B92+1))</f>
         <v/>
       </c>
-      <c r="E92" s="67">
+      <c r="E92" s="68">
         <f>IFERROR(IF($A92="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A92,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F92" s="67">
+      <c r="F92" s="68">
         <f>IFERROR(IF($A92="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A92,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6544,17 +6550,17 @@
     </row>
     <row r="93">
       <c r="A93" s="33" t="n"/>
-      <c r="B93" s="66" t="n"/>
-      <c r="C93" s="66" t="n"/>
+      <c r="B93" s="67" t="n"/>
+      <c r="C93" s="67" t="n"/>
       <c r="D93" s="35">
         <f>IF(OR($B93="",$C93=""),"",IF($C93&lt;$B93,"⚠ dates reversed",$C93-$B93+1))</f>
         <v/>
       </c>
-      <c r="E93" s="67">
+      <c r="E93" s="68">
         <f>IFERROR(IF($A93="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A93,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F93" s="67">
+      <c r="F93" s="68">
         <f>IFERROR(IF($A93="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A93,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6566,17 +6572,17 @@
     </row>
     <row r="94">
       <c r="A94" s="33" t="n"/>
-      <c r="B94" s="66" t="n"/>
-      <c r="C94" s="66" t="n"/>
+      <c r="B94" s="67" t="n"/>
+      <c r="C94" s="67" t="n"/>
       <c r="D94" s="35">
         <f>IF(OR($B94="",$C94=""),"",IF($C94&lt;$B94,"⚠ dates reversed",$C94-$B94+1))</f>
         <v/>
       </c>
-      <c r="E94" s="67">
+      <c r="E94" s="68">
         <f>IFERROR(IF($A94="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A94,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F94" s="67">
+      <c r="F94" s="68">
         <f>IFERROR(IF($A94="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A94,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6588,17 +6594,17 @@
     </row>
     <row r="95">
       <c r="A95" s="33" t="n"/>
-      <c r="B95" s="66" t="n"/>
-      <c r="C95" s="66" t="n"/>
+      <c r="B95" s="67" t="n"/>
+      <c r="C95" s="67" t="n"/>
       <c r="D95" s="35">
         <f>IF(OR($B95="",$C95=""),"",IF($C95&lt;$B95,"⚠ dates reversed",$C95-$B95+1))</f>
         <v/>
       </c>
-      <c r="E95" s="67">
+      <c r="E95" s="68">
         <f>IFERROR(IF($A95="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A95,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F95" s="67">
+      <c r="F95" s="68">
         <f>IFERROR(IF($A95="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A95,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6610,17 +6616,17 @@
     </row>
     <row r="96">
       <c r="A96" s="33" t="n"/>
-      <c r="B96" s="66" t="n"/>
-      <c r="C96" s="66" t="n"/>
+      <c r="B96" s="67" t="n"/>
+      <c r="C96" s="67" t="n"/>
       <c r="D96" s="35">
         <f>IF(OR($B96="",$C96=""),"",IF($C96&lt;$B96,"⚠ dates reversed",$C96-$B96+1))</f>
         <v/>
       </c>
-      <c r="E96" s="67">
+      <c r="E96" s="68">
         <f>IFERROR(IF($A96="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A96,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F96" s="67">
+      <c r="F96" s="68">
         <f>IFERROR(IF($A96="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A96,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6632,17 +6638,17 @@
     </row>
     <row r="97">
       <c r="A97" s="33" t="n"/>
-      <c r="B97" s="66" t="n"/>
-      <c r="C97" s="66" t="n"/>
+      <c r="B97" s="67" t="n"/>
+      <c r="C97" s="67" t="n"/>
       <c r="D97" s="35">
         <f>IF(OR($B97="",$C97=""),"",IF($C97&lt;$B97,"⚠ dates reversed",$C97-$B97+1))</f>
         <v/>
       </c>
-      <c r="E97" s="67">
+      <c r="E97" s="68">
         <f>IFERROR(IF($A97="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A97,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F97" s="67">
+      <c r="F97" s="68">
         <f>IFERROR(IF($A97="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A97,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6654,17 +6660,17 @@
     </row>
     <row r="98">
       <c r="A98" s="33" t="n"/>
-      <c r="B98" s="66" t="n"/>
-      <c r="C98" s="66" t="n"/>
+      <c r="B98" s="67" t="n"/>
+      <c r="C98" s="67" t="n"/>
       <c r="D98" s="35">
         <f>IF(OR($B98="",$C98=""),"",IF($C98&lt;$B98,"⚠ dates reversed",$C98-$B98+1))</f>
         <v/>
       </c>
-      <c r="E98" s="67">
+      <c r="E98" s="68">
         <f>IFERROR(IF($A98="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A98,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F98" s="67">
+      <c r="F98" s="68">
         <f>IFERROR(IF($A98="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A98,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6676,17 +6682,17 @@
     </row>
     <row r="99">
       <c r="A99" s="33" t="n"/>
-      <c r="B99" s="66" t="n"/>
-      <c r="C99" s="66" t="n"/>
+      <c r="B99" s="67" t="n"/>
+      <c r="C99" s="67" t="n"/>
       <c r="D99" s="35">
         <f>IF(OR($B99="",$C99=""),"",IF($C99&lt;$B99,"⚠ dates reversed",$C99-$B99+1))</f>
         <v/>
       </c>
-      <c r="E99" s="67">
+      <c r="E99" s="68">
         <f>IFERROR(IF($A99="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A99,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F99" s="67">
+      <c r="F99" s="68">
         <f>IFERROR(IF($A99="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A99,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6698,17 +6704,17 @@
     </row>
     <row r="100">
       <c r="A100" s="33" t="n"/>
-      <c r="B100" s="66" t="n"/>
-      <c r="C100" s="66" t="n"/>
+      <c r="B100" s="67" t="n"/>
+      <c r="C100" s="67" t="n"/>
       <c r="D100" s="35">
         <f>IF(OR($B100="",$C100=""),"",IF($C100&lt;$B100,"⚠ dates reversed",$C100-$B100+1))</f>
         <v/>
       </c>
-      <c r="E100" s="67">
+      <c r="E100" s="68">
         <f>IFERROR(IF($A100="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A100,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F100" s="67">
+      <c r="F100" s="68">
         <f>IFERROR(IF($A100="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A100,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6720,17 +6726,17 @@
     </row>
     <row r="101">
       <c r="A101" s="33" t="n"/>
-      <c r="B101" s="66" t="n"/>
-      <c r="C101" s="66" t="n"/>
+      <c r="B101" s="67" t="n"/>
+      <c r="C101" s="67" t="n"/>
       <c r="D101" s="35">
         <f>IF(OR($B101="",$C101=""),"",IF($C101&lt;$B101,"⚠ dates reversed",$C101-$B101+1))</f>
         <v/>
       </c>
-      <c r="E101" s="67">
+      <c r="E101" s="68">
         <f>IFERROR(IF($A101="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A101,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F101" s="67">
+      <c r="F101" s="68">
         <f>IFERROR(IF($A101="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A101,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6742,17 +6748,17 @@
     </row>
     <row r="102">
       <c r="A102" s="33" t="n"/>
-      <c r="B102" s="66" t="n"/>
-      <c r="C102" s="66" t="n"/>
+      <c r="B102" s="67" t="n"/>
+      <c r="C102" s="67" t="n"/>
       <c r="D102" s="35">
         <f>IF(OR($B102="",$C102=""),"",IF($C102&lt;$B102,"⚠ dates reversed",$C102-$B102+1))</f>
         <v/>
       </c>
-      <c r="E102" s="67">
+      <c r="E102" s="68">
         <f>IFERROR(IF($A102="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A102,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F102" s="67">
+      <c r="F102" s="68">
         <f>IFERROR(IF($A102="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A102,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6764,17 +6770,17 @@
     </row>
     <row r="103">
       <c r="A103" s="33" t="n"/>
-      <c r="B103" s="66" t="n"/>
-      <c r="C103" s="66" t="n"/>
+      <c r="B103" s="67" t="n"/>
+      <c r="C103" s="67" t="n"/>
       <c r="D103" s="35">
         <f>IF(OR($B103="",$C103=""),"",IF($C103&lt;$B103,"⚠ dates reversed",$C103-$B103+1))</f>
         <v/>
       </c>
-      <c r="E103" s="67">
+      <c r="E103" s="68">
         <f>IFERROR(IF($A103="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A103,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F103" s="67">
+      <c r="F103" s="68">
         <f>IFERROR(IF($A103="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A103,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6786,17 +6792,17 @@
     </row>
     <row r="104">
       <c r="A104" s="33" t="n"/>
-      <c r="B104" s="66" t="n"/>
-      <c r="C104" s="66" t="n"/>
+      <c r="B104" s="67" t="n"/>
+      <c r="C104" s="67" t="n"/>
       <c r="D104" s="35">
         <f>IF(OR($B104="",$C104=""),"",IF($C104&lt;$B104,"⚠ dates reversed",$C104-$B104+1))</f>
         <v/>
       </c>
-      <c r="E104" s="67">
+      <c r="E104" s="68">
         <f>IFERROR(IF($A104="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A104,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F104" s="67">
+      <c r="F104" s="68">
         <f>IFERROR(IF($A104="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A104,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6808,17 +6814,17 @@
     </row>
     <row r="105">
       <c r="A105" s="33" t="n"/>
-      <c r="B105" s="66" t="n"/>
-      <c r="C105" s="66" t="n"/>
+      <c r="B105" s="67" t="n"/>
+      <c r="C105" s="67" t="n"/>
       <c r="D105" s="35">
         <f>IF(OR($B105="",$C105=""),"",IF($C105&lt;$B105,"⚠ dates reversed",$C105-$B105+1))</f>
         <v/>
       </c>
-      <c r="E105" s="67">
+      <c r="E105" s="68">
         <f>IFERROR(IF($A105="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A105,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F105" s="67">
+      <c r="F105" s="68">
         <f>IFERROR(IF($A105="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A105,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6830,17 +6836,17 @@
     </row>
     <row r="106">
       <c r="A106" s="33" t="n"/>
-      <c r="B106" s="66" t="n"/>
-      <c r="C106" s="66" t="n"/>
+      <c r="B106" s="67" t="n"/>
+      <c r="C106" s="67" t="n"/>
       <c r="D106" s="35">
         <f>IF(OR($B106="",$C106=""),"",IF($C106&lt;$B106,"⚠ dates reversed",$C106-$B106+1))</f>
         <v/>
       </c>
-      <c r="E106" s="67">
+      <c r="E106" s="68">
         <f>IFERROR(IF($A106="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A106,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F106" s="67">
+      <c r="F106" s="68">
         <f>IFERROR(IF($A106="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A106,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6852,17 +6858,17 @@
     </row>
     <row r="107">
       <c r="A107" s="33" t="n"/>
-      <c r="B107" s="66" t="n"/>
-      <c r="C107" s="66" t="n"/>
+      <c r="B107" s="67" t="n"/>
+      <c r="C107" s="67" t="n"/>
       <c r="D107" s="35">
         <f>IF(OR($B107="",$C107=""),"",IF($C107&lt;$B107,"⚠ dates reversed",$C107-$B107+1))</f>
         <v/>
       </c>
-      <c r="E107" s="67">
+      <c r="E107" s="68">
         <f>IFERROR(IF($A107="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A107,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F107" s="67">
+      <c r="F107" s="68">
         <f>IFERROR(IF($A107="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A107,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6874,17 +6880,17 @@
     </row>
     <row r="108">
       <c r="A108" s="33" t="n"/>
-      <c r="B108" s="66" t="n"/>
-      <c r="C108" s="66" t="n"/>
+      <c r="B108" s="67" t="n"/>
+      <c r="C108" s="67" t="n"/>
       <c r="D108" s="35">
         <f>IF(OR($B108="",$C108=""),"",IF($C108&lt;$B108,"⚠ dates reversed",$C108-$B108+1))</f>
         <v/>
       </c>
-      <c r="E108" s="67">
+      <c r="E108" s="68">
         <f>IFERROR(IF($A108="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A108,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F108" s="67">
+      <c r="F108" s="68">
         <f>IFERROR(IF($A108="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A108,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6896,17 +6902,17 @@
     </row>
     <row r="109">
       <c r="A109" s="33" t="n"/>
-      <c r="B109" s="66" t="n"/>
-      <c r="C109" s="66" t="n"/>
+      <c r="B109" s="67" t="n"/>
+      <c r="C109" s="67" t="n"/>
       <c r="D109" s="35">
         <f>IF(OR($B109="",$C109=""),"",IF($C109&lt;$B109,"⚠ dates reversed",$C109-$B109+1))</f>
         <v/>
       </c>
-      <c r="E109" s="67">
+      <c r="E109" s="68">
         <f>IFERROR(IF($A109="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A109,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F109" s="67">
+      <c r="F109" s="68">
         <f>IFERROR(IF($A109="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A109,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6918,17 +6924,17 @@
     </row>
     <row r="110">
       <c r="A110" s="33" t="n"/>
-      <c r="B110" s="66" t="n"/>
-      <c r="C110" s="66" t="n"/>
+      <c r="B110" s="67" t="n"/>
+      <c r="C110" s="67" t="n"/>
       <c r="D110" s="35">
         <f>IF(OR($B110="",$C110=""),"",IF($C110&lt;$B110,"⚠ dates reversed",$C110-$B110+1))</f>
         <v/>
       </c>
-      <c r="E110" s="67">
+      <c r="E110" s="68">
         <f>IFERROR(IF($A110="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A110,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F110" s="67">
+      <c r="F110" s="68">
         <f>IFERROR(IF($A110="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A110,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6940,17 +6946,17 @@
     </row>
     <row r="111">
       <c r="A111" s="33" t="n"/>
-      <c r="B111" s="66" t="n"/>
-      <c r="C111" s="66" t="n"/>
+      <c r="B111" s="67" t="n"/>
+      <c r="C111" s="67" t="n"/>
       <c r="D111" s="35">
         <f>IF(OR($B111="",$C111=""),"",IF($C111&lt;$B111,"⚠ dates reversed",$C111-$B111+1))</f>
         <v/>
       </c>
-      <c r="E111" s="67">
+      <c r="E111" s="68">
         <f>IFERROR(IF($A111="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A111,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F111" s="67">
+      <c r="F111" s="68">
         <f>IFERROR(IF($A111="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A111,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6962,17 +6968,17 @@
     </row>
     <row r="112">
       <c r="A112" s="33" t="n"/>
-      <c r="B112" s="66" t="n"/>
-      <c r="C112" s="66" t="n"/>
+      <c r="B112" s="67" t="n"/>
+      <c r="C112" s="67" t="n"/>
       <c r="D112" s="35">
         <f>IF(OR($B112="",$C112=""),"",IF($C112&lt;$B112,"⚠ dates reversed",$C112-$B112+1))</f>
         <v/>
       </c>
-      <c r="E112" s="67">
+      <c r="E112" s="68">
         <f>IFERROR(IF($A112="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A112,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F112" s="67">
+      <c r="F112" s="68">
         <f>IFERROR(IF($A112="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A112,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -6984,17 +6990,17 @@
     </row>
     <row r="113">
       <c r="A113" s="33" t="n"/>
-      <c r="B113" s="66" t="n"/>
-      <c r="C113" s="66" t="n"/>
+      <c r="B113" s="67" t="n"/>
+      <c r="C113" s="67" t="n"/>
       <c r="D113" s="35">
         <f>IF(OR($B113="",$C113=""),"",IF($C113&lt;$B113,"⚠ dates reversed",$C113-$B113+1))</f>
         <v/>
       </c>
-      <c r="E113" s="67">
+      <c r="E113" s="68">
         <f>IFERROR(IF($A113="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A113,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F113" s="67">
+      <c r="F113" s="68">
         <f>IFERROR(IF($A113="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A113,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7006,17 +7012,17 @@
     </row>
     <row r="114">
       <c r="A114" s="33" t="n"/>
-      <c r="B114" s="66" t="n"/>
-      <c r="C114" s="66" t="n"/>
+      <c r="B114" s="67" t="n"/>
+      <c r="C114" s="67" t="n"/>
       <c r="D114" s="35">
         <f>IF(OR($B114="",$C114=""),"",IF($C114&lt;$B114,"⚠ dates reversed",$C114-$B114+1))</f>
         <v/>
       </c>
-      <c r="E114" s="67">
+      <c r="E114" s="68">
         <f>IFERROR(IF($A114="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A114,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F114" s="67">
+      <c r="F114" s="68">
         <f>IFERROR(IF($A114="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A114,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7028,17 +7034,17 @@
     </row>
     <row r="115">
       <c r="A115" s="33" t="n"/>
-      <c r="B115" s="66" t="n"/>
-      <c r="C115" s="66" t="n"/>
+      <c r="B115" s="67" t="n"/>
+      <c r="C115" s="67" t="n"/>
       <c r="D115" s="35">
         <f>IF(OR($B115="",$C115=""),"",IF($C115&lt;$B115,"⚠ dates reversed",$C115-$B115+1))</f>
         <v/>
       </c>
-      <c r="E115" s="67">
+      <c r="E115" s="68">
         <f>IFERROR(IF($A115="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A115,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F115" s="67">
+      <c r="F115" s="68">
         <f>IFERROR(IF($A115="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A115,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7050,17 +7056,17 @@
     </row>
     <row r="116">
       <c r="A116" s="33" t="n"/>
-      <c r="B116" s="66" t="n"/>
-      <c r="C116" s="66" t="n"/>
+      <c r="B116" s="67" t="n"/>
+      <c r="C116" s="67" t="n"/>
       <c r="D116" s="35">
         <f>IF(OR($B116="",$C116=""),"",IF($C116&lt;$B116,"⚠ dates reversed",$C116-$B116+1))</f>
         <v/>
       </c>
-      <c r="E116" s="67">
+      <c r="E116" s="68">
         <f>IFERROR(IF($A116="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A116,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F116" s="67">
+      <c r="F116" s="68">
         <f>IFERROR(IF($A116="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A116,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7072,17 +7078,17 @@
     </row>
     <row r="117">
       <c r="A117" s="33" t="n"/>
-      <c r="B117" s="66" t="n"/>
-      <c r="C117" s="66" t="n"/>
+      <c r="B117" s="67" t="n"/>
+      <c r="C117" s="67" t="n"/>
       <c r="D117" s="35">
         <f>IF(OR($B117="",$C117=""),"",IF($C117&lt;$B117,"⚠ dates reversed",$C117-$B117+1))</f>
         <v/>
       </c>
-      <c r="E117" s="67">
+      <c r="E117" s="68">
         <f>IFERROR(IF($A117="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A117,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F117" s="67">
+      <c r="F117" s="68">
         <f>IFERROR(IF($A117="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A117,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7094,17 +7100,17 @@
     </row>
     <row r="118">
       <c r="A118" s="33" t="n"/>
-      <c r="B118" s="66" t="n"/>
-      <c r="C118" s="66" t="n"/>
+      <c r="B118" s="67" t="n"/>
+      <c r="C118" s="67" t="n"/>
       <c r="D118" s="35">
         <f>IF(OR($B118="",$C118=""),"",IF($C118&lt;$B118,"⚠ dates reversed",$C118-$B118+1))</f>
         <v/>
       </c>
-      <c r="E118" s="67">
+      <c r="E118" s="68">
         <f>IFERROR(IF($A118="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A118,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F118" s="67">
+      <c r="F118" s="68">
         <f>IFERROR(IF($A118="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A118,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7116,17 +7122,17 @@
     </row>
     <row r="119">
       <c r="A119" s="33" t="n"/>
-      <c r="B119" s="66" t="n"/>
-      <c r="C119" s="66" t="n"/>
+      <c r="B119" s="67" t="n"/>
+      <c r="C119" s="67" t="n"/>
       <c r="D119" s="35">
         <f>IF(OR($B119="",$C119=""),"",IF($C119&lt;$B119,"⚠ dates reversed",$C119-$B119+1))</f>
         <v/>
       </c>
-      <c r="E119" s="67">
+      <c r="E119" s="68">
         <f>IFERROR(IF($A119="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A119,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F119" s="67">
+      <c r="F119" s="68">
         <f>IFERROR(IF($A119="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A119,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7138,17 +7144,17 @@
     </row>
     <row r="120">
       <c r="A120" s="33" t="n"/>
-      <c r="B120" s="66" t="n"/>
-      <c r="C120" s="66" t="n"/>
+      <c r="B120" s="67" t="n"/>
+      <c r="C120" s="67" t="n"/>
       <c r="D120" s="35">
         <f>IF(OR($B120="",$C120=""),"",IF($C120&lt;$B120,"⚠ dates reversed",$C120-$B120+1))</f>
         <v/>
       </c>
-      <c r="E120" s="67">
+      <c r="E120" s="68">
         <f>IFERROR(IF($A120="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A120,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F120" s="67">
+      <c r="F120" s="68">
         <f>IFERROR(IF($A120="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A120,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7160,17 +7166,17 @@
     </row>
     <row r="121">
       <c r="A121" s="33" t="n"/>
-      <c r="B121" s="66" t="n"/>
-      <c r="C121" s="66" t="n"/>
+      <c r="B121" s="67" t="n"/>
+      <c r="C121" s="67" t="n"/>
       <c r="D121" s="35">
         <f>IF(OR($B121="",$C121=""),"",IF($C121&lt;$B121,"⚠ dates reversed",$C121-$B121+1))</f>
         <v/>
       </c>
-      <c r="E121" s="67">
+      <c r="E121" s="68">
         <f>IFERROR(IF($A121="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A121,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F121" s="67">
+      <c r="F121" s="68">
         <f>IFERROR(IF($A121="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A121,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7182,17 +7188,17 @@
     </row>
     <row r="122">
       <c r="A122" s="33" t="n"/>
-      <c r="B122" s="66" t="n"/>
-      <c r="C122" s="66" t="n"/>
+      <c r="B122" s="67" t="n"/>
+      <c r="C122" s="67" t="n"/>
       <c r="D122" s="35">
         <f>IF(OR($B122="",$C122=""),"",IF($C122&lt;$B122,"⚠ dates reversed",$C122-$B122+1))</f>
         <v/>
       </c>
-      <c r="E122" s="67">
+      <c r="E122" s="68">
         <f>IFERROR(IF($A122="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A122,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F122" s="67">
+      <c r="F122" s="68">
         <f>IFERROR(IF($A122="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A122,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7204,17 +7210,17 @@
     </row>
     <row r="123">
       <c r="A123" s="33" t="n"/>
-      <c r="B123" s="66" t="n"/>
-      <c r="C123" s="66" t="n"/>
+      <c r="B123" s="67" t="n"/>
+      <c r="C123" s="67" t="n"/>
       <c r="D123" s="35">
         <f>IF(OR($B123="",$C123=""),"",IF($C123&lt;$B123,"⚠ dates reversed",$C123-$B123+1))</f>
         <v/>
       </c>
-      <c r="E123" s="67">
+      <c r="E123" s="68">
         <f>IFERROR(IF($A123="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A123,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F123" s="67">
+      <c r="F123" s="68">
         <f>IFERROR(IF($A123="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A123,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7226,17 +7232,17 @@
     </row>
     <row r="124">
       <c r="A124" s="33" t="n"/>
-      <c r="B124" s="66" t="n"/>
-      <c r="C124" s="66" t="n"/>
+      <c r="B124" s="67" t="n"/>
+      <c r="C124" s="67" t="n"/>
       <c r="D124" s="35">
         <f>IF(OR($B124="",$C124=""),"",IF($C124&lt;$B124,"⚠ dates reversed",$C124-$B124+1))</f>
         <v/>
       </c>
-      <c r="E124" s="67">
+      <c r="E124" s="68">
         <f>IFERROR(IF($A124="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A124,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F124" s="67">
+      <c r="F124" s="68">
         <f>IFERROR(IF($A124="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A124,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7248,17 +7254,17 @@
     </row>
     <row r="125">
       <c r="A125" s="33" t="n"/>
-      <c r="B125" s="66" t="n"/>
-      <c r="C125" s="66" t="n"/>
+      <c r="B125" s="67" t="n"/>
+      <c r="C125" s="67" t="n"/>
       <c r="D125" s="35">
         <f>IF(OR($B125="",$C125=""),"",IF($C125&lt;$B125,"⚠ dates reversed",$C125-$B125+1))</f>
         <v/>
       </c>
-      <c r="E125" s="67">
+      <c r="E125" s="68">
         <f>IFERROR(IF($A125="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A125,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F125" s="67">
+      <c r="F125" s="68">
         <f>IFERROR(IF($A125="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A125,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7270,17 +7276,17 @@
     </row>
     <row r="126">
       <c r="A126" s="33" t="n"/>
-      <c r="B126" s="66" t="n"/>
-      <c r="C126" s="66" t="n"/>
+      <c r="B126" s="67" t="n"/>
+      <c r="C126" s="67" t="n"/>
       <c r="D126" s="35">
         <f>IF(OR($B126="",$C126=""),"",IF($C126&lt;$B126,"⚠ dates reversed",$C126-$B126+1))</f>
         <v/>
       </c>
-      <c r="E126" s="67">
+      <c r="E126" s="68">
         <f>IFERROR(IF($A126="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A126,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F126" s="67">
+      <c r="F126" s="68">
         <f>IFERROR(IF($A126="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A126,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7292,17 +7298,17 @@
     </row>
     <row r="127">
       <c r="A127" s="33" t="n"/>
-      <c r="B127" s="66" t="n"/>
-      <c r="C127" s="66" t="n"/>
+      <c r="B127" s="67" t="n"/>
+      <c r="C127" s="67" t="n"/>
       <c r="D127" s="35">
         <f>IF(OR($B127="",$C127=""),"",IF($C127&lt;$B127,"⚠ dates reversed",$C127-$B127+1))</f>
         <v/>
       </c>
-      <c r="E127" s="67">
+      <c r="E127" s="68">
         <f>IFERROR(IF($A127="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A127,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F127" s="67">
+      <c r="F127" s="68">
         <f>IFERROR(IF($A127="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A127,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7314,17 +7320,17 @@
     </row>
     <row r="128">
       <c r="A128" s="33" t="n"/>
-      <c r="B128" s="66" t="n"/>
-      <c r="C128" s="66" t="n"/>
+      <c r="B128" s="67" t="n"/>
+      <c r="C128" s="67" t="n"/>
       <c r="D128" s="35">
         <f>IF(OR($B128="",$C128=""),"",IF($C128&lt;$B128,"⚠ dates reversed",$C128-$B128+1))</f>
         <v/>
       </c>
-      <c r="E128" s="67">
+      <c r="E128" s="68">
         <f>IFERROR(IF($A128="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A128,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F128" s="67">
+      <c r="F128" s="68">
         <f>IFERROR(IF($A128="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A128,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7336,17 +7342,17 @@
     </row>
     <row r="129">
       <c r="A129" s="33" t="n"/>
-      <c r="B129" s="66" t="n"/>
-      <c r="C129" s="66" t="n"/>
+      <c r="B129" s="67" t="n"/>
+      <c r="C129" s="67" t="n"/>
       <c r="D129" s="35">
         <f>IF(OR($B129="",$C129=""),"",IF($C129&lt;$B129,"⚠ dates reversed",$C129-$B129+1))</f>
         <v/>
       </c>
-      <c r="E129" s="67">
+      <c r="E129" s="68">
         <f>IFERROR(IF($A129="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A129,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F129" s="67">
+      <c r="F129" s="68">
         <f>IFERROR(IF($A129="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A129,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7358,17 +7364,17 @@
     </row>
     <row r="130">
       <c r="A130" s="33" t="n"/>
-      <c r="B130" s="66" t="n"/>
-      <c r="C130" s="66" t="n"/>
+      <c r="B130" s="67" t="n"/>
+      <c r="C130" s="67" t="n"/>
       <c r="D130" s="35">
         <f>IF(OR($B130="",$C130=""),"",IF($C130&lt;$B130,"⚠ dates reversed",$C130-$B130+1))</f>
         <v/>
       </c>
-      <c r="E130" s="67">
+      <c r="E130" s="68">
         <f>IFERROR(IF($A130="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A130,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F130" s="67">
+      <c r="F130" s="68">
         <f>IFERROR(IF($A130="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A130,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7380,17 +7386,17 @@
     </row>
     <row r="131">
       <c r="A131" s="33" t="n"/>
-      <c r="B131" s="66" t="n"/>
-      <c r="C131" s="66" t="n"/>
+      <c r="B131" s="67" t="n"/>
+      <c r="C131" s="67" t="n"/>
       <c r="D131" s="35">
         <f>IF(OR($B131="",$C131=""),"",IF($C131&lt;$B131,"⚠ dates reversed",$C131-$B131+1))</f>
         <v/>
       </c>
-      <c r="E131" s="67">
+      <c r="E131" s="68">
         <f>IFERROR(IF($A131="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A131,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F131" s="67">
+      <c r="F131" s="68">
         <f>IFERROR(IF($A131="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A131,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7402,17 +7408,17 @@
     </row>
     <row r="132">
       <c r="A132" s="33" t="n"/>
-      <c r="B132" s="66" t="n"/>
-      <c r="C132" s="66" t="n"/>
+      <c r="B132" s="67" t="n"/>
+      <c r="C132" s="67" t="n"/>
       <c r="D132" s="35">
         <f>IF(OR($B132="",$C132=""),"",IF($C132&lt;$B132,"⚠ dates reversed",$C132-$B132+1))</f>
         <v/>
       </c>
-      <c r="E132" s="67">
+      <c r="E132" s="68">
         <f>IFERROR(IF($A132="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A132,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F132" s="67">
+      <c r="F132" s="68">
         <f>IFERROR(IF($A132="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A132,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7424,17 +7430,17 @@
     </row>
     <row r="133">
       <c r="A133" s="33" t="n"/>
-      <c r="B133" s="66" t="n"/>
-      <c r="C133" s="66" t="n"/>
+      <c r="B133" s="67" t="n"/>
+      <c r="C133" s="67" t="n"/>
       <c r="D133" s="35">
         <f>IF(OR($B133="",$C133=""),"",IF($C133&lt;$B133,"⚠ dates reversed",$C133-$B133+1))</f>
         <v/>
       </c>
-      <c r="E133" s="67">
+      <c r="E133" s="68">
         <f>IFERROR(IF($A133="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A133,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F133" s="67">
+      <c r="F133" s="68">
         <f>IFERROR(IF($A133="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A133,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7446,17 +7452,17 @@
     </row>
     <row r="134">
       <c r="A134" s="33" t="n"/>
-      <c r="B134" s="66" t="n"/>
-      <c r="C134" s="66" t="n"/>
+      <c r="B134" s="67" t="n"/>
+      <c r="C134" s="67" t="n"/>
       <c r="D134" s="35">
         <f>IF(OR($B134="",$C134=""),"",IF($C134&lt;$B134,"⚠ dates reversed",$C134-$B134+1))</f>
         <v/>
       </c>
-      <c r="E134" s="67">
+      <c r="E134" s="68">
         <f>IFERROR(IF($A134="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A134,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F134" s="67">
+      <c r="F134" s="68">
         <f>IFERROR(IF($A134="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A134,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7468,17 +7474,17 @@
     </row>
     <row r="135">
       <c r="A135" s="33" t="n"/>
-      <c r="B135" s="66" t="n"/>
-      <c r="C135" s="66" t="n"/>
+      <c r="B135" s="67" t="n"/>
+      <c r="C135" s="67" t="n"/>
       <c r="D135" s="35">
         <f>IF(OR($B135="",$C135=""),"",IF($C135&lt;$B135,"⚠ dates reversed",$C135-$B135+1))</f>
         <v/>
       </c>
-      <c r="E135" s="67">
+      <c r="E135" s="68">
         <f>IFERROR(IF($A135="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A135,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F135" s="67">
+      <c r="F135" s="68">
         <f>IFERROR(IF($A135="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A135,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7490,17 +7496,17 @@
     </row>
     <row r="136">
       <c r="A136" s="33" t="n"/>
-      <c r="B136" s="66" t="n"/>
-      <c r="C136" s="66" t="n"/>
+      <c r="B136" s="67" t="n"/>
+      <c r="C136" s="67" t="n"/>
       <c r="D136" s="35">
         <f>IF(OR($B136="",$C136=""),"",IF($C136&lt;$B136,"⚠ dates reversed",$C136-$B136+1))</f>
         <v/>
       </c>
-      <c r="E136" s="67">
+      <c r="E136" s="68">
         <f>IFERROR(IF($A136="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A136,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F136" s="67">
+      <c r="F136" s="68">
         <f>IFERROR(IF($A136="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A136,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7512,17 +7518,17 @@
     </row>
     <row r="137">
       <c r="A137" s="33" t="n"/>
-      <c r="B137" s="66" t="n"/>
-      <c r="C137" s="66" t="n"/>
+      <c r="B137" s="67" t="n"/>
+      <c r="C137" s="67" t="n"/>
       <c r="D137" s="35">
         <f>IF(OR($B137="",$C137=""),"",IF($C137&lt;$B137,"⚠ dates reversed",$C137-$B137+1))</f>
         <v/>
       </c>
-      <c r="E137" s="67">
+      <c r="E137" s="68">
         <f>IFERROR(IF($A137="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A137,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F137" s="67">
+      <c r="F137" s="68">
         <f>IFERROR(IF($A137="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A137,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7534,17 +7540,17 @@
     </row>
     <row r="138">
       <c r="A138" s="33" t="n"/>
-      <c r="B138" s="66" t="n"/>
-      <c r="C138" s="66" t="n"/>
+      <c r="B138" s="67" t="n"/>
+      <c r="C138" s="67" t="n"/>
       <c r="D138" s="35">
         <f>IF(OR($B138="",$C138=""),"",IF($C138&lt;$B138,"⚠ dates reversed",$C138-$B138+1))</f>
         <v/>
       </c>
-      <c r="E138" s="67">
+      <c r="E138" s="68">
         <f>IFERROR(IF($A138="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A138,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F138" s="67">
+      <c r="F138" s="68">
         <f>IFERROR(IF($A138="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A138,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7556,17 +7562,17 @@
     </row>
     <row r="139">
       <c r="A139" s="33" t="n"/>
-      <c r="B139" s="66" t="n"/>
-      <c r="C139" s="66" t="n"/>
+      <c r="B139" s="67" t="n"/>
+      <c r="C139" s="67" t="n"/>
       <c r="D139" s="35">
         <f>IF(OR($B139="",$C139=""),"",IF($C139&lt;$B139,"⚠ dates reversed",$C139-$B139+1))</f>
         <v/>
       </c>
-      <c r="E139" s="67">
+      <c r="E139" s="68">
         <f>IFERROR(IF($A139="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A139,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F139" s="67">
+      <c r="F139" s="68">
         <f>IFERROR(IF($A139="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A139,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7578,17 +7584,17 @@
     </row>
     <row r="140">
       <c r="A140" s="33" t="n"/>
-      <c r="B140" s="66" t="n"/>
-      <c r="C140" s="66" t="n"/>
+      <c r="B140" s="67" t="n"/>
+      <c r="C140" s="67" t="n"/>
       <c r="D140" s="35">
         <f>IF(OR($B140="",$C140=""),"",IF($C140&lt;$B140,"⚠ dates reversed",$C140-$B140+1))</f>
         <v/>
       </c>
-      <c r="E140" s="67">
+      <c r="E140" s="68">
         <f>IFERROR(IF($A140="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A140,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F140" s="67">
+      <c r="F140" s="68">
         <f>IFERROR(IF($A140="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A140,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7600,17 +7606,17 @@
     </row>
     <row r="141">
       <c r="A141" s="33" t="n"/>
-      <c r="B141" s="66" t="n"/>
-      <c r="C141" s="66" t="n"/>
+      <c r="B141" s="67" t="n"/>
+      <c r="C141" s="67" t="n"/>
       <c r="D141" s="35">
         <f>IF(OR($B141="",$C141=""),"",IF($C141&lt;$B141,"⚠ dates reversed",$C141-$B141+1))</f>
         <v/>
       </c>
-      <c r="E141" s="67">
+      <c r="E141" s="68">
         <f>IFERROR(IF($A141="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A141,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F141" s="67">
+      <c r="F141" s="68">
         <f>IFERROR(IF($A141="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A141,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7622,17 +7628,17 @@
     </row>
     <row r="142">
       <c r="A142" s="33" t="n"/>
-      <c r="B142" s="66" t="n"/>
-      <c r="C142" s="66" t="n"/>
+      <c r="B142" s="67" t="n"/>
+      <c r="C142" s="67" t="n"/>
       <c r="D142" s="35">
         <f>IF(OR($B142="",$C142=""),"",IF($C142&lt;$B142,"⚠ dates reversed",$C142-$B142+1))</f>
         <v/>
       </c>
-      <c r="E142" s="67">
+      <c r="E142" s="68">
         <f>IFERROR(IF($A142="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A142,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F142" s="67">
+      <c r="F142" s="68">
         <f>IFERROR(IF($A142="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A142,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7644,17 +7650,17 @@
     </row>
     <row r="143">
       <c r="A143" s="33" t="n"/>
-      <c r="B143" s="66" t="n"/>
-      <c r="C143" s="66" t="n"/>
+      <c r="B143" s="67" t="n"/>
+      <c r="C143" s="67" t="n"/>
       <c r="D143" s="35">
         <f>IF(OR($B143="",$C143=""),"",IF($C143&lt;$B143,"⚠ dates reversed",$C143-$B143+1))</f>
         <v/>
       </c>
-      <c r="E143" s="67">
+      <c r="E143" s="68">
         <f>IFERROR(IF($A143="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A143,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F143" s="67">
+      <c r="F143" s="68">
         <f>IFERROR(IF($A143="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A143,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7666,17 +7672,17 @@
     </row>
     <row r="144">
       <c r="A144" s="33" t="n"/>
-      <c r="B144" s="66" t="n"/>
-      <c r="C144" s="66" t="n"/>
+      <c r="B144" s="67" t="n"/>
+      <c r="C144" s="67" t="n"/>
       <c r="D144" s="35">
         <f>IF(OR($B144="",$C144=""),"",IF($C144&lt;$B144,"⚠ dates reversed",$C144-$B144+1))</f>
         <v/>
       </c>
-      <c r="E144" s="67">
+      <c r="E144" s="68">
         <f>IFERROR(IF($A144="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A144,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F144" s="67">
+      <c r="F144" s="68">
         <f>IFERROR(IF($A144="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A144,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7688,17 +7694,17 @@
     </row>
     <row r="145">
       <c r="A145" s="33" t="n"/>
-      <c r="B145" s="66" t="n"/>
-      <c r="C145" s="66" t="n"/>
+      <c r="B145" s="67" t="n"/>
+      <c r="C145" s="67" t="n"/>
       <c r="D145" s="35">
         <f>IF(OR($B145="",$C145=""),"",IF($C145&lt;$B145,"⚠ dates reversed",$C145-$B145+1))</f>
         <v/>
       </c>
-      <c r="E145" s="67">
+      <c r="E145" s="68">
         <f>IFERROR(IF($A145="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A145,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F145" s="67">
+      <c r="F145" s="68">
         <f>IFERROR(IF($A145="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A145,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7710,17 +7716,17 @@
     </row>
     <row r="146">
       <c r="A146" s="33" t="n"/>
-      <c r="B146" s="66" t="n"/>
-      <c r="C146" s="66" t="n"/>
+      <c r="B146" s="67" t="n"/>
+      <c r="C146" s="67" t="n"/>
       <c r="D146" s="35">
         <f>IF(OR($B146="",$C146=""),"",IF($C146&lt;$B146,"⚠ dates reversed",$C146-$B146+1))</f>
         <v/>
       </c>
-      <c r="E146" s="67">
+      <c r="E146" s="68">
         <f>IFERROR(IF($A146="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A146,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F146" s="67">
+      <c r="F146" s="68">
         <f>IFERROR(IF($A146="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A146,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7732,17 +7738,17 @@
     </row>
     <row r="147">
       <c r="A147" s="33" t="n"/>
-      <c r="B147" s="66" t="n"/>
-      <c r="C147" s="66" t="n"/>
+      <c r="B147" s="67" t="n"/>
+      <c r="C147" s="67" t="n"/>
       <c r="D147" s="35">
         <f>IF(OR($B147="",$C147=""),"",IF($C147&lt;$B147,"⚠ dates reversed",$C147-$B147+1))</f>
         <v/>
       </c>
-      <c r="E147" s="67">
+      <c r="E147" s="68">
         <f>IFERROR(IF($A147="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A147,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F147" s="67">
+      <c r="F147" s="68">
         <f>IFERROR(IF($A147="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A147,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7754,17 +7760,17 @@
     </row>
     <row r="148">
       <c r="A148" s="33" t="n"/>
-      <c r="B148" s="66" t="n"/>
-      <c r="C148" s="66" t="n"/>
+      <c r="B148" s="67" t="n"/>
+      <c r="C148" s="67" t="n"/>
       <c r="D148" s="35">
         <f>IF(OR($B148="",$C148=""),"",IF($C148&lt;$B148,"⚠ dates reversed",$C148-$B148+1))</f>
         <v/>
       </c>
-      <c r="E148" s="67">
+      <c r="E148" s="68">
         <f>IFERROR(IF($A148="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A148,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F148" s="67">
+      <c r="F148" s="68">
         <f>IFERROR(IF($A148="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A148,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7776,17 +7782,17 @@
     </row>
     <row r="149">
       <c r="A149" s="33" t="n"/>
-      <c r="B149" s="66" t="n"/>
-      <c r="C149" s="66" t="n"/>
+      <c r="B149" s="67" t="n"/>
+      <c r="C149" s="67" t="n"/>
       <c r="D149" s="35">
         <f>IF(OR($B149="",$C149=""),"",IF($C149&lt;$B149,"⚠ dates reversed",$C149-$B149+1))</f>
         <v/>
       </c>
-      <c r="E149" s="67">
+      <c r="E149" s="68">
         <f>IFERROR(IF($A149="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A149,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F149" s="67">
+      <c r="F149" s="68">
         <f>IFERROR(IF($A149="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A149,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7798,17 +7804,17 @@
     </row>
     <row r="150">
       <c r="A150" s="33" t="n"/>
-      <c r="B150" s="66" t="n"/>
-      <c r="C150" s="66" t="n"/>
+      <c r="B150" s="67" t="n"/>
+      <c r="C150" s="67" t="n"/>
       <c r="D150" s="35">
         <f>IF(OR($B150="",$C150=""),"",IF($C150&lt;$B150,"⚠ dates reversed",$C150-$B150+1))</f>
         <v/>
       </c>
-      <c r="E150" s="67">
+      <c r="E150" s="68">
         <f>IFERROR(IF($A150="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A150,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F150" s="67">
+      <c r="F150" s="68">
         <f>IFERROR(IF($A150="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A150,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7820,17 +7826,17 @@
     </row>
     <row r="151">
       <c r="A151" s="33" t="n"/>
-      <c r="B151" s="66" t="n"/>
-      <c r="C151" s="66" t="n"/>
+      <c r="B151" s="67" t="n"/>
+      <c r="C151" s="67" t="n"/>
       <c r="D151" s="35">
         <f>IF(OR($B151="",$C151=""),"",IF($C151&lt;$B151,"⚠ dates reversed",$C151-$B151+1))</f>
         <v/>
       </c>
-      <c r="E151" s="67">
+      <c r="E151" s="68">
         <f>IFERROR(IF($A151="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A151,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F151" s="67">
+      <c r="F151" s="68">
         <f>IFERROR(IF($A151="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A151,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7842,17 +7848,17 @@
     </row>
     <row r="152">
       <c r="A152" s="33" t="n"/>
-      <c r="B152" s="66" t="n"/>
-      <c r="C152" s="66" t="n"/>
+      <c r="B152" s="67" t="n"/>
+      <c r="C152" s="67" t="n"/>
       <c r="D152" s="35">
         <f>IF(OR($B152="",$C152=""),"",IF($C152&lt;$B152,"⚠ dates reversed",$C152-$B152+1))</f>
         <v/>
       </c>
-      <c r="E152" s="67">
+      <c r="E152" s="68">
         <f>IFERROR(IF($A152="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A152,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F152" s="67">
+      <c r="F152" s="68">
         <f>IFERROR(IF($A152="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A152,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7864,17 +7870,17 @@
     </row>
     <row r="153">
       <c r="A153" s="33" t="n"/>
-      <c r="B153" s="66" t="n"/>
-      <c r="C153" s="66" t="n"/>
+      <c r="B153" s="67" t="n"/>
+      <c r="C153" s="67" t="n"/>
       <c r="D153" s="35">
         <f>IF(OR($B153="",$C153=""),"",IF($C153&lt;$B153,"⚠ dates reversed",$C153-$B153+1))</f>
         <v/>
       </c>
-      <c r="E153" s="67">
+      <c r="E153" s="68">
         <f>IFERROR(IF($A153="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A153,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F153" s="67">
+      <c r="F153" s="68">
         <f>IFERROR(IF($A153="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A153,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7886,17 +7892,17 @@
     </row>
     <row r="154">
       <c r="A154" s="33" t="n"/>
-      <c r="B154" s="66" t="n"/>
-      <c r="C154" s="66" t="n"/>
+      <c r="B154" s="67" t="n"/>
+      <c r="C154" s="67" t="n"/>
       <c r="D154" s="35">
         <f>IF(OR($B154="",$C154=""),"",IF($C154&lt;$B154,"⚠ dates reversed",$C154-$B154+1))</f>
         <v/>
       </c>
-      <c r="E154" s="67">
+      <c r="E154" s="68">
         <f>IFERROR(IF($A154="","",INDEX('PTO Balance'!$F$5:$F$34,MATCH($A154,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
-      <c r="F154" s="67">
+      <c r="F154" s="68">
         <f>IFERROR(IF($A154="","",INDEX('PTO Balance'!$H$5:$H$34,MATCH($A154,'PTO Balance'!$A$5:$A$34,0))),"")</f>
         <v/>
       </c>
@@ -7957,7 +7963,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G154" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid status" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="kitgp-v2 · Invalid status" prompt="The balance in &quot;PTO Balance&quot; only adds up the days of APPROVED requests, so the text has to come from this list." type="list" errorStyle="stop">
+    <dataValidation sqref="G5:G154" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid status" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="Request status" prompt="The balance in &quot;PTO Balance&quot; only adds up the days of APPROVED requests, so the text has to come from this list." type="list" errorStyle="stop">
       <formula1>"Pending,Approved,Denied"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8015,7 +8021,7 @@
           <t>Year start:</t>
         </is>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="69">
         <f>DATE(YEAR($G$2),1,1)</f>
         <v>46388.0</v>
       </c>
@@ -8024,7 +8030,7 @@
           <t>Year end date:</t>
         </is>
       </c>
-      <c r="G2" s="68">
+      <c r="G2" s="69">
         <f>DATE(YEAR('Annual Calendar'!$B$5),12,31)</f>
         <v>46752.0</v>
       </c>
@@ -8093,22 +8099,22 @@
         <f>IF('Annual Calendar'!$A6="","",'Annual Calendar'!$A6)</f>
         <v/>
       </c>
-      <c r="B5" s="66" t="n"/>
-      <c r="C5" s="66" t="n"/>
+      <c r="B5" s="67" t="n"/>
+      <c r="C5" s="67" t="n"/>
       <c r="D5" s="52" t="n"/>
-      <c r="E5" s="67">
+      <c r="E5" s="68">
         <f>IFERROR(IF($A5="","",MAX(0,MIN(IF($D5="",$B$2,$D5),ROUND(IF($D5="",$B$2,$D5)*((IF($C5="",$G$2,MIN($C5,$G$2)))-(IF($B5="",$E$2,MAX($B5,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F5" s="67">
+      <c r="F5" s="68">
         <f>IF($A5="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A5&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G5" s="67">
+      <c r="G5" s="68">
         <f>IF($A5="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A5&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H5" s="67">
+      <c r="H5" s="68">
         <f>IF($E5="","",ROUND($E5-$F5-$G5,1))</f>
         <v/>
       </c>
@@ -8122,22 +8128,22 @@
         <f>IF('Annual Calendar'!$A7="","",'Annual Calendar'!$A7)</f>
         <v/>
       </c>
-      <c r="B6" s="66" t="n"/>
-      <c r="C6" s="66" t="n"/>
+      <c r="B6" s="67" t="n"/>
+      <c r="C6" s="67" t="n"/>
       <c r="D6" s="52" t="n"/>
-      <c r="E6" s="67">
+      <c r="E6" s="68">
         <f>IFERROR(IF($A6="","",MAX(0,MIN(IF($D6="",$B$2,$D6),ROUND(IF($D6="",$B$2,$D6)*((IF($C6="",$G$2,MIN($C6,$G$2)))-(IF($B6="",$E$2,MAX($B6,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="68">
         <f>IF($A6="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A6&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G6" s="67">
+      <c r="G6" s="68">
         <f>IF($A6="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A6&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H6" s="67">
+      <c r="H6" s="68">
         <f>IF($E6="","",ROUND($E6-$F6-$G6,1))</f>
         <v/>
       </c>
@@ -8151,22 +8157,22 @@
         <f>IF('Annual Calendar'!$A8="","",'Annual Calendar'!$A8)</f>
         <v/>
       </c>
-      <c r="B7" s="66" t="n"/>
-      <c r="C7" s="66" t="n"/>
+      <c r="B7" s="67" t="n"/>
+      <c r="C7" s="67" t="n"/>
       <c r="D7" s="52" t="n"/>
-      <c r="E7" s="67">
+      <c r="E7" s="68">
         <f>IFERROR(IF($A7="","",MAX(0,MIN(IF($D7="",$B$2,$D7),ROUND(IF($D7="",$B$2,$D7)*((IF($C7="",$G$2,MIN($C7,$G$2)))-(IF($B7="",$E$2,MAX($B7,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="67">
+      <c r="F7" s="68">
         <f>IF($A7="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A7&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G7" s="67">
+      <c r="G7" s="68">
         <f>IF($A7="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A7&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H7" s="67">
+      <c r="H7" s="68">
         <f>IF($E7="","",ROUND($E7-$F7-$G7,1))</f>
         <v/>
       </c>
@@ -8180,22 +8186,22 @@
         <f>IF('Annual Calendar'!$A9="","",'Annual Calendar'!$A9)</f>
         <v/>
       </c>
-      <c r="B8" s="66" t="n"/>
-      <c r="C8" s="66" t="n"/>
+      <c r="B8" s="67" t="n"/>
+      <c r="C8" s="67" t="n"/>
       <c r="D8" s="52" t="n"/>
-      <c r="E8" s="67">
+      <c r="E8" s="68">
         <f>IFERROR(IF($A8="","",MAX(0,MIN(IF($D8="",$B$2,$D8),ROUND(IF($D8="",$B$2,$D8)*((IF($C8="",$G$2,MIN($C8,$G$2)))-(IF($B8="",$E$2,MAX($B8,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="68">
         <f>IF($A8="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A8&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G8" s="67">
+      <c r="G8" s="68">
         <f>IF($A8="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A8&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H8" s="67">
+      <c r="H8" s="68">
         <f>IF($E8="","",ROUND($E8-$F8-$G8,1))</f>
         <v/>
       </c>
@@ -8209,22 +8215,22 @@
         <f>IF('Annual Calendar'!$A10="","",'Annual Calendar'!$A10)</f>
         <v/>
       </c>
-      <c r="B9" s="66" t="n"/>
-      <c r="C9" s="66" t="n"/>
+      <c r="B9" s="67" t="n"/>
+      <c r="C9" s="67" t="n"/>
       <c r="D9" s="52" t="n"/>
-      <c r="E9" s="67">
+      <c r="E9" s="68">
         <f>IFERROR(IF($A9="","",MAX(0,MIN(IF($D9="",$B$2,$D9),ROUND(IF($D9="",$B$2,$D9)*((IF($C9="",$G$2,MIN($C9,$G$2)))-(IF($B9="",$E$2,MAX($B9,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="67">
+      <c r="F9" s="68">
         <f>IF($A9="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A9&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="68">
         <f>IF($A9="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A9&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H9" s="67">
+      <c r="H9" s="68">
         <f>IF($E9="","",ROUND($E9-$F9-$G9,1))</f>
         <v/>
       </c>
@@ -8238,22 +8244,22 @@
         <f>IF('Annual Calendar'!$A11="","",'Annual Calendar'!$A11)</f>
         <v/>
       </c>
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
+      <c r="B10" s="67" t="n"/>
+      <c r="C10" s="67" t="n"/>
       <c r="D10" s="52" t="n"/>
-      <c r="E10" s="67">
+      <c r="E10" s="68">
         <f>IFERROR(IF($A10="","",MAX(0,MIN(IF($D10="",$B$2,$D10),ROUND(IF($D10="",$B$2,$D10)*((IF($C10="",$G$2,MIN($C10,$G$2)))-(IF($B10="",$E$2,MAX($B10,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="67">
+      <c r="F10" s="68">
         <f>IF($A10="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A10&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G10" s="67">
+      <c r="G10" s="68">
         <f>IF($A10="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A10&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="68">
         <f>IF($E10="","",ROUND($E10-$F10-$G10,1))</f>
         <v/>
       </c>
@@ -8267,22 +8273,22 @@
         <f>IF('Annual Calendar'!$A12="","",'Annual Calendar'!$A12)</f>
         <v/>
       </c>
-      <c r="B11" s="66" t="n"/>
-      <c r="C11" s="66" t="n"/>
+      <c r="B11" s="67" t="n"/>
+      <c r="C11" s="67" t="n"/>
       <c r="D11" s="52" t="n"/>
-      <c r="E11" s="67">
+      <c r="E11" s="68">
         <f>IFERROR(IF($A11="","",MAX(0,MIN(IF($D11="",$B$2,$D11),ROUND(IF($D11="",$B$2,$D11)*((IF($C11="",$G$2,MIN($C11,$G$2)))-(IF($B11="",$E$2,MAX($B11,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="67">
+      <c r="F11" s="68">
         <f>IF($A11="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A11&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="68">
         <f>IF($A11="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A11&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H11" s="67">
+      <c r="H11" s="68">
         <f>IF($E11="","",ROUND($E11-$F11-$G11,1))</f>
         <v/>
       </c>
@@ -8296,22 +8302,22 @@
         <f>IF('Annual Calendar'!$A13="","",'Annual Calendar'!$A13)</f>
         <v/>
       </c>
-      <c r="B12" s="66" t="n"/>
-      <c r="C12" s="66" t="n"/>
+      <c r="B12" s="67" t="n"/>
+      <c r="C12" s="67" t="n"/>
       <c r="D12" s="52" t="n"/>
-      <c r="E12" s="67">
+      <c r="E12" s="68">
         <f>IFERROR(IF($A12="","",MAX(0,MIN(IF($D12="",$B$2,$D12),ROUND(IF($D12="",$B$2,$D12)*((IF($C12="",$G$2,MIN($C12,$G$2)))-(IF($B12="",$E$2,MAX($B12,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F12" s="67">
+      <c r="F12" s="68">
         <f>IF($A12="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A12&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G12" s="67">
+      <c r="G12" s="68">
         <f>IF($A12="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A12&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H12" s="67">
+      <c r="H12" s="68">
         <f>IF($E12="","",ROUND($E12-$F12-$G12,1))</f>
         <v/>
       </c>
@@ -8325,22 +8331,22 @@
         <f>IF('Annual Calendar'!$A14="","",'Annual Calendar'!$A14)</f>
         <v/>
       </c>
-      <c r="B13" s="66" t="n"/>
-      <c r="C13" s="66" t="n"/>
+      <c r="B13" s="67" t="n"/>
+      <c r="C13" s="67" t="n"/>
       <c r="D13" s="52" t="n"/>
-      <c r="E13" s="67">
+      <c r="E13" s="68">
         <f>IFERROR(IF($A13="","",MAX(0,MIN(IF($D13="",$B$2,$D13),ROUND(IF($D13="",$B$2,$D13)*((IF($C13="",$G$2,MIN($C13,$G$2)))-(IF($B13="",$E$2,MAX($B13,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F13" s="67">
+      <c r="F13" s="68">
         <f>IF($A13="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A13&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G13" s="67">
+      <c r="G13" s="68">
         <f>IF($A13="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A13&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H13" s="67">
+      <c r="H13" s="68">
         <f>IF($E13="","",ROUND($E13-$F13-$G13,1))</f>
         <v/>
       </c>
@@ -8354,22 +8360,22 @@
         <f>IF('Annual Calendar'!$A15="","",'Annual Calendar'!$A15)</f>
         <v/>
       </c>
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
+      <c r="B14" s="67" t="n"/>
+      <c r="C14" s="67" t="n"/>
       <c r="D14" s="52" t="n"/>
-      <c r="E14" s="67">
+      <c r="E14" s="68">
         <f>IFERROR(IF($A14="","",MAX(0,MIN(IF($D14="",$B$2,$D14),ROUND(IF($D14="",$B$2,$D14)*((IF($C14="",$G$2,MIN($C14,$G$2)))-(IF($B14="",$E$2,MAX($B14,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F14" s="67">
+      <c r="F14" s="68">
         <f>IF($A14="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A14&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G14" s="67">
+      <c r="G14" s="68">
         <f>IF($A14="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A14&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H14" s="67">
+      <c r="H14" s="68">
         <f>IF($E14="","",ROUND($E14-$F14-$G14,1))</f>
         <v/>
       </c>
@@ -8383,22 +8389,22 @@
         <f>IF('Annual Calendar'!$A16="","",'Annual Calendar'!$A16)</f>
         <v/>
       </c>
-      <c r="B15" s="66" t="n"/>
-      <c r="C15" s="66" t="n"/>
+      <c r="B15" s="67" t="n"/>
+      <c r="C15" s="67" t="n"/>
       <c r="D15" s="52" t="n"/>
-      <c r="E15" s="67">
+      <c r="E15" s="68">
         <f>IFERROR(IF($A15="","",MAX(0,MIN(IF($D15="",$B$2,$D15),ROUND(IF($D15="",$B$2,$D15)*((IF($C15="",$G$2,MIN($C15,$G$2)))-(IF($B15="",$E$2,MAX($B15,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="68">
         <f>IF($A15="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A15&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="68">
         <f>IF($A15="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A15&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H15" s="67">
+      <c r="H15" s="68">
         <f>IF($E15="","",ROUND($E15-$F15-$G15,1))</f>
         <v/>
       </c>
@@ -8412,22 +8418,22 @@
         <f>IF('Annual Calendar'!$A17="","",'Annual Calendar'!$A17)</f>
         <v/>
       </c>
-      <c r="B16" s="66" t="n"/>
-      <c r="C16" s="66" t="n"/>
+      <c r="B16" s="67" t="n"/>
+      <c r="C16" s="67" t="n"/>
       <c r="D16" s="52" t="n"/>
-      <c r="E16" s="67">
+      <c r="E16" s="68">
         <f>IFERROR(IF($A16="","",MAX(0,MIN(IF($D16="",$B$2,$D16),ROUND(IF($D16="",$B$2,$D16)*((IF($C16="",$G$2,MIN($C16,$G$2)))-(IF($B16="",$E$2,MAX($B16,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="68">
         <f>IF($A16="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A16&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G16" s="67">
+      <c r="G16" s="68">
         <f>IF($A16="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A16&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H16" s="67">
+      <c r="H16" s="68">
         <f>IF($E16="","",ROUND($E16-$F16-$G16,1))</f>
         <v/>
       </c>
@@ -8441,22 +8447,22 @@
         <f>IF('Annual Calendar'!$A18="","",'Annual Calendar'!$A18)</f>
         <v/>
       </c>
-      <c r="B17" s="66" t="n"/>
-      <c r="C17" s="66" t="n"/>
+      <c r="B17" s="67" t="n"/>
+      <c r="C17" s="67" t="n"/>
       <c r="D17" s="52" t="n"/>
-      <c r="E17" s="67">
+      <c r="E17" s="68">
         <f>IFERROR(IF($A17="","",MAX(0,MIN(IF($D17="",$B$2,$D17),ROUND(IF($D17="",$B$2,$D17)*((IF($C17="",$G$2,MIN($C17,$G$2)))-(IF($B17="",$E$2,MAX($B17,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="68">
         <f>IF($A17="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A17&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G17" s="67">
+      <c r="G17" s="68">
         <f>IF($A17="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A17&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H17" s="67">
+      <c r="H17" s="68">
         <f>IF($E17="","",ROUND($E17-$F17-$G17,1))</f>
         <v/>
       </c>
@@ -8470,22 +8476,22 @@
         <f>IF('Annual Calendar'!$A19="","",'Annual Calendar'!$A19)</f>
         <v/>
       </c>
-      <c r="B18" s="66" t="n"/>
-      <c r="C18" s="66" t="n"/>
+      <c r="B18" s="67" t="n"/>
+      <c r="C18" s="67" t="n"/>
       <c r="D18" s="52" t="n"/>
-      <c r="E18" s="67">
+      <c r="E18" s="68">
         <f>IFERROR(IF($A18="","",MAX(0,MIN(IF($D18="",$B$2,$D18),ROUND(IF($D18="",$B$2,$D18)*((IF($C18="",$G$2,MIN($C18,$G$2)))-(IF($B18="",$E$2,MAX($B18,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F18" s="67">
+      <c r="F18" s="68">
         <f>IF($A18="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A18&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G18" s="67">
+      <c r="G18" s="68">
         <f>IF($A18="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A18&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H18" s="67">
+      <c r="H18" s="68">
         <f>IF($E18="","",ROUND($E18-$F18-$G18,1))</f>
         <v/>
       </c>
@@ -8499,22 +8505,22 @@
         <f>IF('Annual Calendar'!$A20="","",'Annual Calendar'!$A20)</f>
         <v/>
       </c>
-      <c r="B19" s="66" t="n"/>
-      <c r="C19" s="66" t="n"/>
+      <c r="B19" s="67" t="n"/>
+      <c r="C19" s="67" t="n"/>
       <c r="D19" s="52" t="n"/>
-      <c r="E19" s="67">
+      <c r="E19" s="68">
         <f>IFERROR(IF($A19="","",MAX(0,MIN(IF($D19="",$B$2,$D19),ROUND(IF($D19="",$B$2,$D19)*((IF($C19="",$G$2,MIN($C19,$G$2)))-(IF($B19="",$E$2,MAX($B19,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="68">
         <f>IF($A19="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A19&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G19" s="67">
+      <c r="G19" s="68">
         <f>IF($A19="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A19&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H19" s="67">
+      <c r="H19" s="68">
         <f>IF($E19="","",ROUND($E19-$F19-$G19,1))</f>
         <v/>
       </c>
@@ -8528,22 +8534,22 @@
         <f>IF('Annual Calendar'!$A21="","",'Annual Calendar'!$A21)</f>
         <v/>
       </c>
-      <c r="B20" s="66" t="n"/>
-      <c r="C20" s="66" t="n"/>
+      <c r="B20" s="67" t="n"/>
+      <c r="C20" s="67" t="n"/>
       <c r="D20" s="52" t="n"/>
-      <c r="E20" s="67">
+      <c r="E20" s="68">
         <f>IFERROR(IF($A20="","",MAX(0,MIN(IF($D20="",$B$2,$D20),ROUND(IF($D20="",$B$2,$D20)*((IF($C20="",$G$2,MIN($C20,$G$2)))-(IF($B20="",$E$2,MAX($B20,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F20" s="67">
+      <c r="F20" s="68">
         <f>IF($A20="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A20&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G20" s="67">
+      <c r="G20" s="68">
         <f>IF($A20="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A20&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H20" s="67">
+      <c r="H20" s="68">
         <f>IF($E20="","",ROUND($E20-$F20-$G20,1))</f>
         <v/>
       </c>
@@ -8557,22 +8563,22 @@
         <f>IF('Annual Calendar'!$A22="","",'Annual Calendar'!$A22)</f>
         <v/>
       </c>
-      <c r="B21" s="66" t="n"/>
-      <c r="C21" s="66" t="n"/>
+      <c r="B21" s="67" t="n"/>
+      <c r="C21" s="67" t="n"/>
       <c r="D21" s="52" t="n"/>
-      <c r="E21" s="67">
+      <c r="E21" s="68">
         <f>IFERROR(IF($A21="","",MAX(0,MIN(IF($D21="",$B$2,$D21),ROUND(IF($D21="",$B$2,$D21)*((IF($C21="",$G$2,MIN($C21,$G$2)))-(IF($B21="",$E$2,MAX($B21,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F21" s="67">
+      <c r="F21" s="68">
         <f>IF($A21="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A21&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G21" s="67">
+      <c r="G21" s="68">
         <f>IF($A21="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A21&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H21" s="67">
+      <c r="H21" s="68">
         <f>IF($E21="","",ROUND($E21-$F21-$G21,1))</f>
         <v/>
       </c>
@@ -8586,22 +8592,22 @@
         <f>IF('Annual Calendar'!$A23="","",'Annual Calendar'!$A23)</f>
         <v/>
       </c>
-      <c r="B22" s="66" t="n"/>
-      <c r="C22" s="66" t="n"/>
+      <c r="B22" s="67" t="n"/>
+      <c r="C22" s="67" t="n"/>
       <c r="D22" s="52" t="n"/>
-      <c r="E22" s="67">
+      <c r="E22" s="68">
         <f>IFERROR(IF($A22="","",MAX(0,MIN(IF($D22="",$B$2,$D22),ROUND(IF($D22="",$B$2,$D22)*((IF($C22="",$G$2,MIN($C22,$G$2)))-(IF($B22="",$E$2,MAX($B22,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F22" s="67">
+      <c r="F22" s="68">
         <f>IF($A22="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A22&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G22" s="67">
+      <c r="G22" s="68">
         <f>IF($A22="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A22&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H22" s="67">
+      <c r="H22" s="68">
         <f>IF($E22="","",ROUND($E22-$F22-$G22,1))</f>
         <v/>
       </c>
@@ -8615,22 +8621,22 @@
         <f>IF('Annual Calendar'!$A24="","",'Annual Calendar'!$A24)</f>
         <v/>
       </c>
-      <c r="B23" s="66" t="n"/>
-      <c r="C23" s="66" t="n"/>
+      <c r="B23" s="67" t="n"/>
+      <c r="C23" s="67" t="n"/>
       <c r="D23" s="52" t="n"/>
-      <c r="E23" s="67">
+      <c r="E23" s="68">
         <f>IFERROR(IF($A23="","",MAX(0,MIN(IF($D23="",$B$2,$D23),ROUND(IF($D23="",$B$2,$D23)*((IF($C23="",$G$2,MIN($C23,$G$2)))-(IF($B23="",$E$2,MAX($B23,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F23" s="67">
+      <c r="F23" s="68">
         <f>IF($A23="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A23&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G23" s="67">
+      <c r="G23" s="68">
         <f>IF($A23="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A23&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H23" s="67">
+      <c r="H23" s="68">
         <f>IF($E23="","",ROUND($E23-$F23-$G23,1))</f>
         <v/>
       </c>
@@ -8644,22 +8650,22 @@
         <f>IF('Annual Calendar'!$A25="","",'Annual Calendar'!$A25)</f>
         <v/>
       </c>
-      <c r="B24" s="66" t="n"/>
-      <c r="C24" s="66" t="n"/>
+      <c r="B24" s="67" t="n"/>
+      <c r="C24" s="67" t="n"/>
       <c r="D24" s="52" t="n"/>
-      <c r="E24" s="67">
+      <c r="E24" s="68">
         <f>IFERROR(IF($A24="","",MAX(0,MIN(IF($D24="",$B$2,$D24),ROUND(IF($D24="",$B$2,$D24)*((IF($C24="",$G$2,MIN($C24,$G$2)))-(IF($B24="",$E$2,MAX($B24,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F24" s="67">
+      <c r="F24" s="68">
         <f>IF($A24="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A24&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G24" s="67">
+      <c r="G24" s="68">
         <f>IF($A24="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A24&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H24" s="67">
+      <c r="H24" s="68">
         <f>IF($E24="","",ROUND($E24-$F24-$G24,1))</f>
         <v/>
       </c>
@@ -8673,22 +8679,22 @@
         <f>IF('Annual Calendar'!$A26="","",'Annual Calendar'!$A26)</f>
         <v/>
       </c>
-      <c r="B25" s="66" t="n"/>
-      <c r="C25" s="66" t="n"/>
+      <c r="B25" s="67" t="n"/>
+      <c r="C25" s="67" t="n"/>
       <c r="D25" s="52" t="n"/>
-      <c r="E25" s="67">
+      <c r="E25" s="68">
         <f>IFERROR(IF($A25="","",MAX(0,MIN(IF($D25="",$B$2,$D25),ROUND(IF($D25="",$B$2,$D25)*((IF($C25="",$G$2,MIN($C25,$G$2)))-(IF($B25="",$E$2,MAX($B25,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F25" s="67">
+      <c r="F25" s="68">
         <f>IF($A25="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A25&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G25" s="67">
+      <c r="G25" s="68">
         <f>IF($A25="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A25&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H25" s="67">
+      <c r="H25" s="68">
         <f>IF($E25="","",ROUND($E25-$F25-$G25,1))</f>
         <v/>
       </c>
@@ -8702,22 +8708,22 @@
         <f>IF('Annual Calendar'!$A27="","",'Annual Calendar'!$A27)</f>
         <v/>
       </c>
-      <c r="B26" s="66" t="n"/>
-      <c r="C26" s="66" t="n"/>
+      <c r="B26" s="67" t="n"/>
+      <c r="C26" s="67" t="n"/>
       <c r="D26" s="52" t="n"/>
-      <c r="E26" s="67">
+      <c r="E26" s="68">
         <f>IFERROR(IF($A26="","",MAX(0,MIN(IF($D26="",$B$2,$D26),ROUND(IF($D26="",$B$2,$D26)*((IF($C26="",$G$2,MIN($C26,$G$2)))-(IF($B26="",$E$2,MAX($B26,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F26" s="67">
+      <c r="F26" s="68">
         <f>IF($A26="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A26&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G26" s="67">
+      <c r="G26" s="68">
         <f>IF($A26="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A26&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H26" s="67">
+      <c r="H26" s="68">
         <f>IF($E26="","",ROUND($E26-$F26-$G26,1))</f>
         <v/>
       </c>
@@ -8731,22 +8737,22 @@
         <f>IF('Annual Calendar'!$A28="","",'Annual Calendar'!$A28)</f>
         <v/>
       </c>
-      <c r="B27" s="66" t="n"/>
-      <c r="C27" s="66" t="n"/>
+      <c r="B27" s="67" t="n"/>
+      <c r="C27" s="67" t="n"/>
       <c r="D27" s="52" t="n"/>
-      <c r="E27" s="67">
+      <c r="E27" s="68">
         <f>IFERROR(IF($A27="","",MAX(0,MIN(IF($D27="",$B$2,$D27),ROUND(IF($D27="",$B$2,$D27)*((IF($C27="",$G$2,MIN($C27,$G$2)))-(IF($B27="",$E$2,MAX($B27,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="68">
         <f>IF($A27="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A27&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G27" s="67">
+      <c r="G27" s="68">
         <f>IF($A27="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A27&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H27" s="67">
+      <c r="H27" s="68">
         <f>IF($E27="","",ROUND($E27-$F27-$G27,1))</f>
         <v/>
       </c>
@@ -8760,22 +8766,22 @@
         <f>IF('Annual Calendar'!$A29="","",'Annual Calendar'!$A29)</f>
         <v/>
       </c>
-      <c r="B28" s="66" t="n"/>
-      <c r="C28" s="66" t="n"/>
+      <c r="B28" s="67" t="n"/>
+      <c r="C28" s="67" t="n"/>
       <c r="D28" s="52" t="n"/>
-      <c r="E28" s="67">
+      <c r="E28" s="68">
         <f>IFERROR(IF($A28="","",MAX(0,MIN(IF($D28="",$B$2,$D28),ROUND(IF($D28="",$B$2,$D28)*((IF($C28="",$G$2,MIN($C28,$G$2)))-(IF($B28="",$E$2,MAX($B28,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F28" s="67">
+      <c r="F28" s="68">
         <f>IF($A28="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A28&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G28" s="67">
+      <c r="G28" s="68">
         <f>IF($A28="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A28&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H28" s="67">
+      <c r="H28" s="68">
         <f>IF($E28="","",ROUND($E28-$F28-$G28,1))</f>
         <v/>
       </c>
@@ -8789,22 +8795,22 @@
         <f>IF('Annual Calendar'!$A30="","",'Annual Calendar'!$A30)</f>
         <v/>
       </c>
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
+      <c r="B29" s="67" t="n"/>
+      <c r="C29" s="67" t="n"/>
       <c r="D29" s="52" t="n"/>
-      <c r="E29" s="67">
+      <c r="E29" s="68">
         <f>IFERROR(IF($A29="","",MAX(0,MIN(IF($D29="",$B$2,$D29),ROUND(IF($D29="",$B$2,$D29)*((IF($C29="",$G$2,MIN($C29,$G$2)))-(IF($B29="",$E$2,MAX($B29,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F29" s="67">
+      <c r="F29" s="68">
         <f>IF($A29="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A29&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G29" s="67">
+      <c r="G29" s="68">
         <f>IF($A29="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A29&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H29" s="67">
+      <c r="H29" s="68">
         <f>IF($E29="","",ROUND($E29-$F29-$G29,1))</f>
         <v/>
       </c>
@@ -8818,22 +8824,22 @@
         <f>IF('Annual Calendar'!$A31="","",'Annual Calendar'!$A31)</f>
         <v/>
       </c>
-      <c r="B30" s="66" t="n"/>
-      <c r="C30" s="66" t="n"/>
+      <c r="B30" s="67" t="n"/>
+      <c r="C30" s="67" t="n"/>
       <c r="D30" s="52" t="n"/>
-      <c r="E30" s="67">
+      <c r="E30" s="68">
         <f>IFERROR(IF($A30="","",MAX(0,MIN(IF($D30="",$B$2,$D30),ROUND(IF($D30="",$B$2,$D30)*((IF($C30="",$G$2,MIN($C30,$G$2)))-(IF($B30="",$E$2,MAX($B30,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F30" s="67">
+      <c r="F30" s="68">
         <f>IF($A30="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A30&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G30" s="67">
+      <c r="G30" s="68">
         <f>IF($A30="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A30&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H30" s="67">
+      <c r="H30" s="68">
         <f>IF($E30="","",ROUND($E30-$F30-$G30,1))</f>
         <v/>
       </c>
@@ -8847,22 +8853,22 @@
         <f>IF('Annual Calendar'!$A32="","",'Annual Calendar'!$A32)</f>
         <v/>
       </c>
-      <c r="B31" s="66" t="n"/>
-      <c r="C31" s="66" t="n"/>
+      <c r="B31" s="67" t="n"/>
+      <c r="C31" s="67" t="n"/>
       <c r="D31" s="52" t="n"/>
-      <c r="E31" s="67">
+      <c r="E31" s="68">
         <f>IFERROR(IF($A31="","",MAX(0,MIN(IF($D31="",$B$2,$D31),ROUND(IF($D31="",$B$2,$D31)*((IF($C31="",$G$2,MIN($C31,$G$2)))-(IF($B31="",$E$2,MAX($B31,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F31" s="67">
+      <c r="F31" s="68">
         <f>IF($A31="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A31&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G31" s="67">
+      <c r="G31" s="68">
         <f>IF($A31="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A31&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H31" s="67">
+      <c r="H31" s="68">
         <f>IF($E31="","",ROUND($E31-$F31-$G31,1))</f>
         <v/>
       </c>
@@ -8876,22 +8882,22 @@
         <f>IF('Annual Calendar'!$A33="","",'Annual Calendar'!$A33)</f>
         <v/>
       </c>
-      <c r="B32" s="66" t="n"/>
-      <c r="C32" s="66" t="n"/>
+      <c r="B32" s="67" t="n"/>
+      <c r="C32" s="67" t="n"/>
       <c r="D32" s="52" t="n"/>
-      <c r="E32" s="67">
+      <c r="E32" s="68">
         <f>IFERROR(IF($A32="","",MAX(0,MIN(IF($D32="",$B$2,$D32),ROUND(IF($D32="",$B$2,$D32)*((IF($C32="",$G$2,MIN($C32,$G$2)))-(IF($B32="",$E$2,MAX($B32,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F32" s="67">
+      <c r="F32" s="68">
         <f>IF($A32="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A32&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G32" s="67">
+      <c r="G32" s="68">
         <f>IF($A32="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A32&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H32" s="67">
+      <c r="H32" s="68">
         <f>IF($E32="","",ROUND($E32-$F32-$G32,1))</f>
         <v/>
       </c>
@@ -8905,22 +8911,22 @@
         <f>IF('Annual Calendar'!$A34="","",'Annual Calendar'!$A34)</f>
         <v/>
       </c>
-      <c r="B33" s="66" t="n"/>
-      <c r="C33" s="66" t="n"/>
+      <c r="B33" s="67" t="n"/>
+      <c r="C33" s="67" t="n"/>
       <c r="D33" s="52" t="n"/>
-      <c r="E33" s="67">
+      <c r="E33" s="68">
         <f>IFERROR(IF($A33="","",MAX(0,MIN(IF($D33="",$B$2,$D33),ROUND(IF($D33="",$B$2,$D33)*((IF($C33="",$G$2,MIN($C33,$G$2)))-(IF($B33="",$E$2,MAX($B33,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F33" s="67">
+      <c r="F33" s="68">
         <f>IF($A33="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A33&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G33" s="67">
+      <c r="G33" s="68">
         <f>IF($A33="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A33&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H33" s="67">
+      <c r="H33" s="68">
         <f>IF($E33="","",ROUND($E33-$F33-$G33,1))</f>
         <v/>
       </c>
@@ -8934,22 +8940,22 @@
         <f>IF('Annual Calendar'!$A35="","",'Annual Calendar'!$A35)</f>
         <v/>
       </c>
-      <c r="B34" s="66" t="n"/>
-      <c r="C34" s="66" t="n"/>
+      <c r="B34" s="67" t="n"/>
+      <c r="C34" s="67" t="n"/>
       <c r="D34" s="52" t="n"/>
-      <c r="E34" s="67">
+      <c r="E34" s="68">
         <f>IFERROR(IF($A34="","",MAX(0,MIN(IF($D34="",$B$2,$D34),ROUND(IF($D34="",$B$2,$D34)*((IF($C34="",$G$2,MIN($C34,$G$2)))-(IF($B34="",$E$2,MAX($B34,$E$2)))+1)/($G$2-$E$2+1),1)))),"")</f>
         <v/>
       </c>
-      <c r="F34" s="67">
+      <c r="F34" s="68">
         <f>IF($A34="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A34&amp;"",'PTO Requests'!$G$5:$G$154,"Approved",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="G34" s="67">
+      <c r="G34" s="68">
         <f>IF($A34="","",SUMIFS('PTO Requests'!$D$5:$D$154,'PTO Requests'!$A$5:$A$154,$A34&amp;"",'PTO Requests'!$G$5:$G$154,"Pending",'PTO Requests'!$B$5:$B$154,"&gt;="&amp;'PTO Balance'!$E$2,'PTO Requests'!$B$5:$B$154,"&lt;="&amp;'PTO Balance'!$G$2))</f>
         <v/>
       </c>
-      <c r="H34" s="67">
+      <c r="H34" s="68">
         <f>IF($E34="","",ROUND($E34-$F34-$G34,1))</f>
         <v/>
       </c>
@@ -8968,7 +8974,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="51" t="inlineStr">
         <is>
-          <t>▸ Proration is linear over the days the person is on staff WITHIN the year: both the hire date and the end date count. A seasonal worker from January to June earns 7 days, not 14 — and that is the number that goes into the final paycheck. Your policy may count whole months: in that case type the days that apply in "Own days".</t>
+          <t>▸ Proration is linear over the days the person is on staff WITHIN the year: both the hire date and the end date count. A seasonal worker from January to June earns 7 days, not 14 — check it against your state's final-pay rule and your own PTO policy. Your policy may count whole months: in that case type the days that apply in "Own days".</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9009,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · pto_days" prompt="Federal law sets no PTO minimum: type your policy (default 14 calendar days = two weeks). If your policy is in workdays (10 for two weeks), type 10 and count only workdays in the requests. UK: 5.6 weeks (39 calendar days)."/>
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="PTO days per year" prompt="Federal law sets no PTO minimum: type your policy (default 14 calendar days = two weeks). If your policy is in workdays (10 for two weeks), type 10 and count only workdays in the requests. UK: 5.6 weeks (39 calendar days)."/>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -9171,7 +9177,7 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="51" t="inlineStr">
         <is>
-          <t>▸ Above the maximum in B3 the "Coverage" row of the calendar turns amber; in high season the threshold is the one in D3. The minimums per shift are the ones file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)) and BONUS-02 use for the default case (5 people per service): they are a starting point, adjust them to your menu. And they are not decorative: the last indicator below counts the weeks when available staff does not reach the most demanding shift.</t>
+          <t>▸ Above the maximum in B3 the "Coverage" row of the calendar turns amber; in high season the threshold is the one in D3. The minimums per shift are the ones file 03 "Restaurant Labor Cost Calculator" and BONUS-02 use for the default case (5 people per service): they are a starting point, adjust them to your menu. And they are not decorative: the last indicator below counts the weeks when available staff does not reach the most demanding shift.</t>
         </is>
       </c>
     </row>
@@ -9731,8 +9737,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="70" t="inlineStr">
         <is>
           <t>Weeks when the most demanding shift is NOT covered (staff − absences &lt; minimum):</t>
         </is>
@@ -9780,7 +9786,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B12:B41" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid position" error="Pick the position of the absent person." promptTitle="kitgp-v2b · Invalid position" prompt="The position decides who can cover whom: a busser cannot cover a head chef. If one is missing, unprotect the sheet and edit the list." type="list" errorStyle="stop">
+    <dataValidation sqref="B12:B41" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid position" error="Pick the position of the absent person." promptTitle="Position" prompt="The position decides who can cover whom: a busser cannot cover a head chef. If one is missing, unprotect the sheet and edit the list." type="list" errorStyle="stop">
       <formula1>"Head chef,Sous chef,Line cook,Prep cook,Pastry cook,Dishwasher,FOH manager,Server,Busser,Bartender,Sommelier,Host,Delivery driver,Shift manager"</formula1>
     </dataValidation>
   </dataValidations>
